--- a/src/components/Roster/filled.xlsx
+++ b/src/components/Roster/filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYPRO\Roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE116D5-6561-4836-85DC-A000423B7751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA99B8-F01F-4C22-8F52-78A858D77FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97B97223-865E-45D4-9E75-2997D7267C15}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="IV" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">III!$A$1:$Q$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">IV!$A$1:$Q$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">III!$A$1:$R$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">IV!$A$1:$R$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="62">
   <si>
     <t>SC</t>
   </si>
@@ -228,12 +228,15 @@
   <si>
     <t>Vidut Sahayyak</t>
   </si>
+  <si>
+    <t>SURPLUS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,13 +302,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="13"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -344,12 +340,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -422,47 +418,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -561,51 +516,23 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -624,6 +551,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -980,19 +937,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="47" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="38" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="38.85546875" customWidth="1"/>
     <col min="4" max="4" width="36.7109375" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
@@ -1038,15 +994,18 @@
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+    <row r="2" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="17"/>
@@ -1087,15 +1046,17 @@
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>48</v>
-      </c>
-      <c r="P2" s="3">
-        <v>48</v>
-      </c>
-      <c r="Q2" s="8"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="3">
+        <f>SUM(E2:P2)</f>
+        <v>50</v>
+      </c>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="17"/>
@@ -1138,13 +1099,15 @@
       <c r="O3" s="13">
         <v>1</v>
       </c>
-      <c r="P3" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="8"/>
-    </row>
-    <row r="4" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="P3" s="13"/>
+      <c r="Q3" s="3">
+        <f t="shared" ref="Q3:Q59" si="0">SUM(E3:P3)</f>
+        <v>2</v>
+      </c>
+      <c r="R3" s="8"/>
+    </row>
+    <row r="4" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="17"/>
@@ -1187,13 +1150,15 @@
       <c r="O4" s="5">
         <v>8</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="3">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q4" s="6"/>
-    </row>
-    <row r="5" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="17"/>
@@ -1236,13 +1201,15 @@
       <c r="O5" s="13">
         <v>2</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q5" s="6"/>
-    </row>
-    <row r="6" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="17"/>
@@ -1274,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -1283,16 +1250,17 @@
         <v>2</v>
       </c>
       <c r="O6" s="5">
-        <v>19</v>
-      </c>
-      <c r="P6" s="3">
-        <f t="shared" ref="P6:P7" si="0">SUM(E6:O6)</f>
+        <v>18</v>
+      </c>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="3">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="Q6" s="8"/>
-    </row>
-    <row r="7" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="R6" s="8"/>
+    </row>
+    <row r="7" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="17"/>
@@ -1335,16 +1303,17 @@
       <c r="O7" s="5">
         <v>0</v>
       </c>
-      <c r="P7" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="8" t="s">
+      <c r="P7" s="5"/>
+      <c r="Q7" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="17"/>
@@ -1354,46 +1323,48 @@
       <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="14">
-        <v>2</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14">
-        <v>0</v>
-      </c>
-      <c r="J8" s="14">
-        <v>0</v>
-      </c>
-      <c r="K8" s="14">
-        <v>0</v>
-      </c>
-      <c r="L8" s="14">
-        <v>0</v>
-      </c>
-      <c r="M8" s="14">
-        <v>0</v>
-      </c>
-      <c r="N8" s="14">
-        <v>0</v>
-      </c>
-      <c r="O8" s="14">
+      <c r="E8" s="13">
+        <v>2</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13">
         <v>3</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="13"/>
+      <c r="Q8" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q8" s="8"/>
-    </row>
-    <row r="9" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="17"/>
@@ -1403,46 +1374,48 @@
       <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6">
+      <c r="E9" s="13">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13">
         <v>4</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="13"/>
+      <c r="Q9" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q9" s="8"/>
-    </row>
-    <row r="10" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="17"/>
@@ -1483,16 +1456,17 @@
         <v>0</v>
       </c>
       <c r="O10" s="5">
-        <v>23</v>
-      </c>
-      <c r="P10" s="14">
-        <f t="shared" ref="P10:P11" si="1">SUM(E10:O10)</f>
-        <v>42</v>
-      </c>
-      <c r="Q10" s="8"/>
-    </row>
-    <row r="11" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="17"/>
@@ -1535,16 +1509,17 @@
       <c r="O11" s="5">
         <v>0</v>
       </c>
-      <c r="P11" s="14">
-        <f t="shared" si="1"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="R11" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="17"/>
@@ -1587,13 +1562,15 @@
       <c r="O12" s="14">
         <v>0</v>
       </c>
-      <c r="P12" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8"/>
-    </row>
-    <row r="13" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="P12" s="14"/>
+      <c r="Q12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="17"/>
@@ -1636,13 +1613,15 @@
       <c r="O13" s="5">
         <v>7</v>
       </c>
-      <c r="P13" s="14">
+      <c r="P13" s="5"/>
+      <c r="Q13" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="Q13" s="8"/>
-    </row>
-    <row r="14" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A14" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="17"/>
@@ -1650,13 +1629,13 @@
         <v>25</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
       </c>
       <c r="F14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
@@ -1685,13 +1664,15 @@
       <c r="O14" s="6">
         <v>20</v>
       </c>
-      <c r="P14" s="14">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="6"/>
-    </row>
-    <row r="15" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
+      <c r="P14" s="6"/>
+      <c r="Q14" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="17"/>
@@ -1699,7 +1680,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E15" s="6">
         <v>8</v>
@@ -1732,15 +1713,17 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>96</v>
-      </c>
-      <c r="P15" s="14">
-        <v>114</v>
-      </c>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="3">
+        <f t="shared" si="0"/>
+        <v>137</v>
+      </c>
+      <c r="R15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="17"/>
@@ -1748,10 +1731,10 @@
         <v>18</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E16" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6">
         <v>3</v>
@@ -1781,15 +1764,17 @@
         <v>0</v>
       </c>
       <c r="O16" s="6">
-        <v>33</v>
-      </c>
-      <c r="P16" s="14">
-        <v>43</v>
-      </c>
-      <c r="Q16" s="6"/>
-    </row>
-    <row r="17" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A17" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="17"/>
@@ -1797,10 +1782,10 @@
         <v>19</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E17" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6">
         <v>0</v>
@@ -1815,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6">
         <v>1</v>
@@ -1830,15 +1815,17 @@
         <v>0</v>
       </c>
       <c r="O17" s="6">
-        <v>40</v>
-      </c>
-      <c r="P17" s="14">
+        <v>42</v>
+      </c>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="3">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="Q17" s="6"/>
-    </row>
-    <row r="18" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44" t="s">
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="17"/>
@@ -1849,16 +1836,16 @@
         <v>51</v>
       </c>
       <c r="E18" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" s="5">
         <v>8</v>
       </c>
       <c r="G18" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H18" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5">
         <v>4</v>
@@ -1870,25 +1857,26 @@
         <v>3</v>
       </c>
       <c r="L18" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M18" s="5">
         <v>7</v>
       </c>
       <c r="N18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="5">
-        <v>76</v>
-      </c>
-      <c r="P18" s="3">
-        <f t="shared" ref="P18" si="2">SUM(E18:O18)</f>
-        <v>144</v>
-      </c>
-      <c r="Q18" s="8"/>
-    </row>
-    <row r="19" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="3">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="17"/>
@@ -1931,16 +1919,17 @@
       <c r="O19" s="5">
         <v>1</v>
       </c>
-      <c r="P19" s="3">
-        <f t="shared" ref="P19" si="3">SUM(E19:O19)</f>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="8" t="s">
+      <c r="P19" s="5"/>
+      <c r="Q19" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+    <row r="20" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="17"/>
@@ -1983,13 +1972,15 @@
       <c r="O20" s="11">
         <v>0</v>
       </c>
-      <c r="P20" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="8"/>
-    </row>
-    <row r="21" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="45" t="s">
+      <c r="P20" s="11"/>
+      <c r="Q20" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R20" s="8"/>
+    </row>
+    <row r="21" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="18"/>
@@ -2000,25 +1991,25 @@
         <v>13</v>
       </c>
       <c r="E21" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="5">
         <v>1</v>
       </c>
       <c r="H21" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
         <v>0</v>
@@ -2030,15 +2021,17 @@
         <v>0</v>
       </c>
       <c r="O21" s="5">
-        <v>29</v>
-      </c>
-      <c r="P21" s="3">
+        <v>39</v>
+      </c>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="3">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="Q21" s="8"/>
-    </row>
-    <row r="22" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="18"/>
@@ -2048,46 +2041,48 @@
       <c r="D22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="5">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <v>1</v>
-      </c>
-      <c r="M22" s="5">
-        <v>1</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1</v>
-      </c>
-      <c r="O22" s="5">
-        <v>2</v>
-      </c>
-      <c r="P22" s="3">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="8"/>
-    </row>
-    <row r="23" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
+        <v>5</v>
+      </c>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="R22" s="8"/>
+    </row>
+    <row r="23" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="18"/>
@@ -2128,15 +2123,17 @@
         <v>0</v>
       </c>
       <c r="O23" s="5">
+        <v>10</v>
+      </c>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="3">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P23" s="3">
-        <v>12</v>
-      </c>
-      <c r="Q23" s="8"/>
-    </row>
-    <row r="24" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="45" t="s">
+      <c r="R23" s="8"/>
+    </row>
+    <row r="24" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="18"/>
@@ -2179,13 +2176,15 @@
       <c r="O24" s="13">
         <v>0</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="8"/>
-    </row>
-    <row r="25" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
+      <c r="P24" s="13"/>
+      <c r="Q24" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="8"/>
+    </row>
+    <row r="25" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="18"/>
@@ -2228,14 +2227,15 @@
       <c r="O25" s="5">
         <v>14</v>
       </c>
-      <c r="P25" s="29">
-        <f>SUM(E25:O25)</f>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="3">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="Q25" s="8"/>
-    </row>
-    <row r="26" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+      <c r="R25" s="8"/>
+    </row>
+    <row r="26" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="18"/>
@@ -2263,8 +2263,8 @@
       <c r="J26" s="5">
         <v>0</v>
       </c>
-      <c r="K26" s="5">
-        <v>1</v>
+      <c r="K26" s="39">
+        <v>0</v>
       </c>
       <c r="L26" s="5">
         <v>1</v>
@@ -2278,16 +2278,17 @@
       <c r="O26" s="5">
         <v>2</v>
       </c>
-      <c r="P26" s="29">
-        <f>SUM(E26:O26)</f>
-        <v>6</v>
-      </c>
-      <c r="Q26" s="8" t="s">
+      <c r="P26" s="34"/>
+      <c r="Q26" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="R26" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
+    <row r="27" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="18"/>
@@ -2330,13 +2331,15 @@
       <c r="O27" s="14">
         <v>2</v>
       </c>
-      <c r="P27" s="14">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="8"/>
-    </row>
-    <row r="28" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45" t="s">
+      <c r="P27" s="14"/>
+      <c r="Q27" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R27" s="8"/>
+    </row>
+    <row r="28" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="18"/>
@@ -2379,13 +2382,15 @@
       <c r="O28" s="6">
         <v>3</v>
       </c>
-      <c r="P28" s="14">
+      <c r="P28" s="6"/>
+      <c r="Q28" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Q28" s="8"/>
-    </row>
-    <row r="29" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="45" t="s">
+      <c r="R28" s="8"/>
+    </row>
+    <row r="29" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="18"/>
@@ -2416,8 +2421,8 @@
       <c r="K29" s="5">
         <v>0</v>
       </c>
-      <c r="L29" s="5">
-        <v>5</v>
+      <c r="L29" s="39">
+        <v>6</v>
       </c>
       <c r="M29" s="5">
         <v>0</v>
@@ -2428,14 +2433,15 @@
       <c r="O29" s="5">
         <v>20</v>
       </c>
-      <c r="P29" s="3">
-        <f t="shared" ref="P29:P30" si="4">SUM(E29:O29)</f>
-        <v>36</v>
-      </c>
-      <c r="Q29" s="8"/>
-    </row>
-    <row r="30" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="P29" s="5"/>
+      <c r="Q29" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="R29" s="8"/>
+    </row>
+    <row r="30" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="18"/>
@@ -2466,8 +2472,8 @@
       <c r="K30" s="5">
         <v>0</v>
       </c>
-      <c r="L30" s="5">
-        <v>3</v>
+      <c r="L30" s="39">
+        <v>4</v>
       </c>
       <c r="M30" s="5">
         <v>2</v>
@@ -2478,16 +2484,17 @@
       <c r="O30" s="5">
         <v>1</v>
       </c>
-      <c r="P30" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="Q30" s="8" t="s">
+      <c r="P30" s="5"/>
+      <c r="Q30" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="R30" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
+    <row r="31" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="18"/>
@@ -2530,13 +2537,15 @@
       <c r="O31" s="14">
         <v>0</v>
       </c>
-      <c r="P31" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="8"/>
-    </row>
-    <row r="32" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
+      <c r="P31" s="14"/>
+      <c r="Q31" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R31" s="8"/>
+    </row>
+    <row r="32" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="18"/>
@@ -2544,7 +2553,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E32" s="5">
         <v>0</v>
@@ -2579,13 +2588,15 @@
       <c r="O32" s="5">
         <v>7</v>
       </c>
-      <c r="P32" s="14">
+      <c r="P32" s="5"/>
+      <c r="Q32" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="Q32" s="8"/>
-    </row>
-    <row r="33" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
+      <c r="R32" s="8"/>
+    </row>
+    <row r="33" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A33" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="18"/>
@@ -2593,7 +2604,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E33" s="6">
         <v>1</v>
@@ -2628,13 +2639,15 @@
       <c r="O33" s="6">
         <v>16</v>
       </c>
-      <c r="P33" s="14">
+      <c r="P33" s="6"/>
+      <c r="Q33" s="3">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="Q33" s="8"/>
-    </row>
-    <row r="34" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
+      <c r="R33" s="8"/>
+    </row>
+    <row r="34" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A34" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="18"/>
@@ -2642,7 +2655,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E34" s="6">
         <v>6</v>
@@ -2677,13 +2690,15 @@
       <c r="O34" s="6">
         <v>103</v>
       </c>
-      <c r="P34" s="14">
+      <c r="P34" s="6"/>
+      <c r="Q34" s="3">
+        <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="Q34" s="8"/>
-    </row>
-    <row r="35" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
+      <c r="R34" s="8"/>
+    </row>
+    <row r="35" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="18"/>
@@ -2691,7 +2706,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E35" s="6">
         <v>2</v>
@@ -2726,13 +2741,15 @@
       <c r="O35" s="6">
         <v>38</v>
       </c>
-      <c r="P35" s="14">
+      <c r="P35" s="6"/>
+      <c r="Q35" s="3">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="Q35" s="8"/>
-    </row>
-    <row r="36" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="45" t="s">
+      <c r="R35" s="8"/>
+    </row>
+    <row r="36" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="18"/>
@@ -2740,7 +2757,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E36" s="6">
         <v>2</v>
@@ -2775,13 +2792,15 @@
       <c r="O36" s="6">
         <v>37</v>
       </c>
-      <c r="P36" s="14">
+      <c r="P36" s="6"/>
+      <c r="Q36" s="3">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="Q36" s="8"/>
-    </row>
-    <row r="37" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
+      <c r="R36" s="8"/>
+    </row>
+    <row r="37" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="18"/>
@@ -2792,46 +2811,47 @@
         <v>51</v>
       </c>
       <c r="E37" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F37" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="5">
         <v>5</v>
       </c>
       <c r="K37" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M37" s="5">
         <v>0</v>
       </c>
       <c r="N37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="5">
-        <v>76</v>
-      </c>
-      <c r="P37" s="3">
-        <f t="shared" ref="P37:P38" si="5">SUM(E37:O37)</f>
-        <v>145</v>
-      </c>
-      <c r="Q37" s="8"/>
-    </row>
-    <row r="38" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="3">
+        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+      <c r="R37" s="8"/>
+    </row>
+    <row r="38" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B38" s="18"/>
@@ -2874,16 +2894,17 @@
       <c r="O38" s="5">
         <v>2</v>
       </c>
-      <c r="P38" s="3">
-        <f t="shared" si="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Q38" s="8" t="s">
+      <c r="R38" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
+    <row r="39" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B39" s="18"/>
@@ -2926,13 +2947,15 @@
       <c r="O39" s="14">
         <v>0</v>
       </c>
-      <c r="P39" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="8"/>
-    </row>
-    <row r="40" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="46" t="s">
+      <c r="P39" s="14"/>
+      <c r="Q39" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R39" s="8"/>
+    </row>
+    <row r="40" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="19"/>
@@ -2973,15 +2996,17 @@
         <v>0</v>
       </c>
       <c r="O40" s="10">
-        <v>38</v>
-      </c>
-      <c r="P40" s="3">
-        <v>39</v>
-      </c>
-      <c r="Q40" s="8"/>
-    </row>
-    <row r="41" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A41" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="R40" s="43"/>
+    </row>
+    <row r="41" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A41" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="19"/>
@@ -3024,13 +3049,15 @@
       <c r="O41" s="13">
         <v>0</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="8"/>
-    </row>
-    <row r="42" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="46" t="s">
+      <c r="P41" s="13"/>
+      <c r="Q41" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="43"/>
+    </row>
+    <row r="42" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="19"/>
@@ -3073,13 +3100,15 @@
       <c r="O42" s="5">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="5"/>
+      <c r="Q42" s="3">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Q42" s="8"/>
-    </row>
-    <row r="43" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A43" s="46" t="s">
+      <c r="R42" s="43"/>
+    </row>
+    <row r="43" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A43" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="19"/>
@@ -3122,13 +3151,15 @@
       <c r="O43" s="13">
         <v>0</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="8"/>
-    </row>
-    <row r="44" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="46" t="s">
+      <c r="P43" s="13"/>
+      <c r="Q43" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="43"/>
+    </row>
+    <row r="44" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="19"/>
@@ -3138,7 +3169,7 @@
       <c r="D44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="10">
         <v>2</v>
       </c>
       <c r="F44" s="10">
@@ -3160,25 +3191,26 @@
         <v>0</v>
       </c>
       <c r="L44" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="10">
         <v>0</v>
       </c>
       <c r="N44" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="10">
         <v>7</v>
       </c>
-      <c r="P44" s="30">
-        <f t="shared" ref="P44:P45" si="6">SUM(E44:O44)</f>
-        <v>12</v>
-      </c>
-      <c r="Q44" s="8"/>
-    </row>
-    <row r="45" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="46" t="s">
+      <c r="P44" s="10"/>
+      <c r="Q44" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R44" s="43"/>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="19"/>
@@ -3188,7 +3220,7 @@
       <c r="D45" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="10">
         <v>0</v>
       </c>
       <c r="F45" s="10">
@@ -3210,27 +3242,28 @@
         <v>0</v>
       </c>
       <c r="L45" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="10">
         <v>0</v>
       </c>
       <c r="N45" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="10">
-        <v>0</v>
-      </c>
-      <c r="P45" s="30">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="R45" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="46" t="s">
+    <row r="46" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="19"/>
@@ -3273,13 +3306,15 @@
       <c r="O46" s="15">
         <v>0</v>
       </c>
-      <c r="P46" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="8"/>
-    </row>
-    <row r="47" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="46" t="s">
+      <c r="P46" s="15"/>
+      <c r="Q46" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="43"/>
+    </row>
+    <row r="47" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B47" s="19"/>
@@ -3322,13 +3357,15 @@
       <c r="O47" s="10">
         <v>2</v>
       </c>
-      <c r="P47" s="15">
-        <v>2</v>
-      </c>
-      <c r="Q47" s="8"/>
-    </row>
-    <row r="48" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="46" t="s">
+      <c r="P47" s="10"/>
+      <c r="Q47" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R47" s="43"/>
+    </row>
+    <row r="48" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B48" s="19"/>
@@ -3342,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="10">
         <v>0</v>
@@ -3369,16 +3406,17 @@
         <v>0</v>
       </c>
       <c r="O48" s="10">
-        <v>12</v>
-      </c>
-      <c r="P48" s="3">
-        <f t="shared" ref="P48:P49" si="7">SUM(E48:O48)</f>
-        <v>14</v>
-      </c>
-      <c r="Q48" s="8"/>
-    </row>
-    <row r="49" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="R48" s="43"/>
+    </row>
+    <row r="49" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B49" s="19"/>
@@ -3419,18 +3457,19 @@
         <v>0</v>
       </c>
       <c r="O49" s="5">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3">
-        <f t="shared" si="7"/>
-        <v>19</v>
-      </c>
-      <c r="Q49" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R49" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="46" t="s">
+    <row r="50" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B50" s="19"/>
@@ -3442,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5">
         <v>0</v>
@@ -3471,16 +3510,19 @@
       <c r="O50" s="5">
         <v>0</v>
       </c>
-      <c r="P50" s="3">
-        <f>SUM(E50:O50)</f>
-        <v>1</v>
-      </c>
-      <c r="Q50" s="8" t="s">
+      <c r="P50" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R50" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="46" t="s">
+    <row r="51" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B51" s="19"/>
@@ -3523,13 +3565,15 @@
       <c r="O51" s="9">
         <v>0</v>
       </c>
-      <c r="P51" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="8"/>
-    </row>
-    <row r="52" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
+      <c r="P51" s="9"/>
+      <c r="Q51" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R51" s="43"/>
+    </row>
+    <row r="52" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B52" s="19"/>
@@ -3572,13 +3616,15 @@
       <c r="O52" s="9">
         <v>0</v>
       </c>
-      <c r="P52" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="8"/>
-    </row>
-    <row r="53" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="46" t="s">
+      <c r="P52" s="9"/>
+      <c r="Q52" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R52" s="43"/>
+    </row>
+    <row r="53" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B53" s="19"/>
@@ -3588,46 +3634,50 @@
       <c r="D53" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E53" s="6">
-        <v>0</v>
-      </c>
-      <c r="F53" s="6">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6">
-        <v>0</v>
-      </c>
-      <c r="J53" s="6">
-        <v>0</v>
-      </c>
-      <c r="K53" s="6">
-        <v>0</v>
-      </c>
-      <c r="L53" s="6">
-        <v>0</v>
-      </c>
-      <c r="M53" s="6">
-        <v>0</v>
-      </c>
-      <c r="N53" s="6">
-        <v>0</v>
-      </c>
-      <c r="O53" s="6">
+      <c r="E53" s="40">
+        <v>0</v>
+      </c>
+      <c r="F53" s="40">
+        <v>0</v>
+      </c>
+      <c r="G53" s="40">
+        <v>0</v>
+      </c>
+      <c r="H53" s="40">
+        <v>0</v>
+      </c>
+      <c r="I53" s="40">
+        <v>0</v>
+      </c>
+      <c r="J53" s="40">
+        <v>0</v>
+      </c>
+      <c r="K53" s="40">
+        <v>0</v>
+      </c>
+      <c r="L53" s="40">
+        <v>0</v>
+      </c>
+      <c r="M53" s="40">
+        <v>0</v>
+      </c>
+      <c r="N53" s="40">
+        <v>0</v>
+      </c>
+      <c r="O53" s="40">
         <v>22</v>
       </c>
       <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="Q53" s="8"/>
-    </row>
-    <row r="54" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A54" s="46" t="s">
+      <c r="R53" s="43"/>
+    </row>
+    <row r="54" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A54" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B54" s="19"/>
@@ -3670,13 +3720,15 @@
       <c r="O54" s="6">
         <v>74</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="6"/>
+      <c r="Q54" s="3">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="Q54" s="8"/>
-    </row>
-    <row r="55" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A55" s="46" t="s">
+      <c r="R54" s="43"/>
+    </row>
+    <row r="55" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A55" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B55" s="19"/>
@@ -3717,15 +3769,17 @@
         <v>0</v>
       </c>
       <c r="O55" s="6">
-        <v>31</v>
-      </c>
-      <c r="P55" s="3">
-        <v>37</v>
-      </c>
-      <c r="Q55" s="8"/>
-    </row>
-    <row r="56" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A56" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="R55" s="43"/>
+    </row>
+    <row r="56" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A56" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B56" s="19"/>
@@ -3766,15 +3820,17 @@
         <v>0</v>
       </c>
       <c r="O56" s="6">
-        <v>33</v>
-      </c>
-      <c r="P56" s="3">
-        <v>38</v>
-      </c>
-      <c r="Q56" s="8"/>
-    </row>
-    <row r="57" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="R56" s="43"/>
+    </row>
+    <row r="57" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B57" s="19"/>
@@ -3785,28 +3841,28 @@
         <v>51</v>
       </c>
       <c r="E57" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G57" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H57" s="10">
         <v>0</v>
       </c>
       <c r="I57" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" s="10">
         <v>2</v>
       </c>
       <c r="K57" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M57" s="10">
         <v>0</v>
@@ -3815,16 +3871,17 @@
         <v>4</v>
       </c>
       <c r="O57" s="10">
-        <v>26</v>
-      </c>
-      <c r="P57" s="30">
-        <f t="shared" ref="P57:P58" si="8">SUM(E57:O57)</f>
-        <v>70</v>
-      </c>
-      <c r="Q57" s="8"/>
-    </row>
-    <row r="58" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="R57" s="43"/>
+    </row>
+    <row r="58" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B58" s="19"/>
@@ -3834,49 +3891,50 @@
       <c r="D58" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="31">
-        <v>0</v>
-      </c>
-      <c r="F58" s="31">
-        <v>0</v>
-      </c>
-      <c r="G58" s="31">
-        <v>0</v>
-      </c>
-      <c r="H58" s="31">
-        <v>0</v>
-      </c>
-      <c r="I58" s="31">
-        <v>0</v>
-      </c>
-      <c r="J58" s="31">
-        <v>0</v>
-      </c>
-      <c r="K58" s="31">
-        <v>0</v>
-      </c>
-      <c r="L58" s="31">
-        <v>0</v>
-      </c>
-      <c r="M58" s="31">
-        <v>0</v>
-      </c>
-      <c r="N58" s="31">
-        <v>0</v>
-      </c>
-      <c r="O58" s="31">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="8" t="s">
+      <c r="E58" s="29">
+        <v>0</v>
+      </c>
+      <c r="F58" s="29">
+        <v>0</v>
+      </c>
+      <c r="G58" s="29">
+        <v>0</v>
+      </c>
+      <c r="H58" s="29">
+        <v>0</v>
+      </c>
+      <c r="I58" s="29">
+        <v>0</v>
+      </c>
+      <c r="J58" s="29">
+        <v>0</v>
+      </c>
+      <c r="K58" s="29">
+        <v>0</v>
+      </c>
+      <c r="L58" s="29">
+        <v>0</v>
+      </c>
+      <c r="M58" s="29">
+        <v>0</v>
+      </c>
+      <c r="N58" s="29">
+        <v>0</v>
+      </c>
+      <c r="O58" s="29">
+        <v>0</v>
+      </c>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A59" s="46" t="s">
+    <row r="59" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A59" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B59" s="19"/>
@@ -3920,18 +3978,16 @@
         <v>1</v>
       </c>
       <c r="P59" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R59" s="43"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q59" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PRC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R59" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3939,8 +3995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -3949,60 +4004,63 @@
     <col min="4" max="4" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:18" s="47" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -4048,13 +4106,14 @@
       <c r="O2" s="20">
         <v>3</v>
       </c>
-      <c r="P2" s="21">
-        <f t="shared" ref="P2:P25" si="0">SUM(E2:O2)</f>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="21">
+        <f>SUM(E2:P2)</f>
         <v>8</v>
       </c>
-      <c r="Q2" s="8"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -4100,15 +4159,16 @@
       <c r="O3" s="20">
         <v>0</v>
       </c>
-      <c r="P3" s="21">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Q3" s="8" t="s">
+      <c r="P3" s="41"/>
+      <c r="Q3" s="21">
+        <f t="shared" ref="Q3:Q66" si="0">SUM(E3:P3)</f>
+        <v>2</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -4131,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -4149,18 +4209,19 @@
         <v>0</v>
       </c>
       <c r="N4" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="20">
         <v>4</v>
       </c>
-      <c r="P4" s="21">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="41"/>
+      <c r="Q4" s="21">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="R4" s="8"/>
+    </row>
+    <row r="5" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -4183,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -4197,24 +4258,25 @@
       <c r="L5" s="5">
         <v>0</v>
       </c>
-      <c r="M5" s="20">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0</v>
-      </c>
-      <c r="P5" s="21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="8" t="s">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -4260,13 +4322,14 @@
       <c r="O6" s="20">
         <v>5</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="41"/>
+      <c r="Q6" s="21">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="Q6" s="8"/>
-    </row>
-    <row r="7" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="8"/>
+    </row>
+    <row r="7" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -4312,15 +4375,16 @@
       <c r="O7" s="20">
         <v>0</v>
       </c>
-      <c r="P7" s="21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="8" t="s">
+      <c r="P7" s="41"/>
+      <c r="Q7" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -4361,18 +4425,19 @@
         <v>0</v>
       </c>
       <c r="N8" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="20">
         <v>4</v>
       </c>
-      <c r="P8" s="21">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="Q8" s="8"/>
-    </row>
-    <row r="9" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="41"/>
+      <c r="Q8" s="21">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -4407,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="20">
         <v>0</v>
@@ -4418,15 +4483,16 @@
       <c r="O9" s="20">
         <v>0</v>
       </c>
-      <c r="P9" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8" t="s">
+      <c r="P9" s="41"/>
+      <c r="Q9" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -4472,13 +4538,14 @@
       <c r="O10" s="20">
         <v>4</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="41"/>
+      <c r="Q10" s="21">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="Q10" s="8"/>
-    </row>
-    <row r="11" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -4524,15 +4591,16 @@
       <c r="O11" s="20">
         <v>0</v>
       </c>
-      <c r="P11" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8" t="s">
+      <c r="P11" s="41"/>
+      <c r="Q11" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -4573,18 +4641,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="5">
         <v>4</v>
       </c>
-      <c r="P12" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Q12" s="8"/>
-    </row>
-    <row r="13" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="5"/>
+      <c r="Q12" s="21">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -4630,15 +4699,16 @@
       <c r="O13" s="20">
         <v>0</v>
       </c>
-      <c r="P13" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8" t="s">
+      <c r="P13" s="20"/>
+      <c r="Q13" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -4684,13 +4754,14 @@
       <c r="O14" s="5">
         <v>4</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="5"/>
+      <c r="Q14" s="21">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="Q14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -4736,15 +4807,16 @@
       <c r="O15" s="20">
         <v>0</v>
       </c>
-      <c r="P15" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="8" t="s">
+      <c r="P15" s="20"/>
+      <c r="Q15" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -4790,13 +4862,14 @@
       <c r="O16" s="5">
         <v>3</v>
       </c>
-      <c r="P16" s="7">
+      <c r="P16" s="5"/>
+      <c r="Q16" s="21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="Q16" s="8"/>
-    </row>
-    <row r="17" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
@@ -4842,15 +4915,16 @@
       <c r="O17" s="20">
         <v>0</v>
       </c>
-      <c r="P17" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Q17" s="8" t="s">
+      <c r="P17" s="20"/>
+      <c r="Q17" s="21">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
@@ -4896,13 +4970,14 @@
       <c r="O18" s="5">
         <v>4</v>
       </c>
-      <c r="P18" s="7">
+      <c r="P18" s="5"/>
+      <c r="Q18" s="21">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Q18" s="8"/>
-    </row>
-    <row r="19" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -4948,15 +5023,16 @@
       <c r="O19" s="20">
         <v>0</v>
       </c>
-      <c r="P19" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8" t="s">
+      <c r="P19" s="20"/>
+      <c r="Q19" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -5002,13 +5078,14 @@
       <c r="O20" s="5">
         <v>0</v>
       </c>
-      <c r="P20" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8"/>
-    </row>
-    <row r="21" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P20" s="5"/>
+      <c r="Q20" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="8"/>
+    </row>
+    <row r="21" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -5054,15 +5131,16 @@
       <c r="O21" s="5">
         <v>0</v>
       </c>
-      <c r="P21" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8" t="s">
+      <c r="P21" s="5"/>
+      <c r="Q21" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -5108,13 +5186,14 @@
       <c r="O22" s="5">
         <v>0</v>
       </c>
-      <c r="P22" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8"/>
-    </row>
-    <row r="23" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P22" s="5"/>
+      <c r="Q22" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="8"/>
+    </row>
+    <row r="23" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -5160,15 +5239,16 @@
       <c r="O23" s="5">
         <v>0</v>
       </c>
-      <c r="P23" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8" t="s">
+      <c r="P23" s="5"/>
+      <c r="Q23" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -5214,13 +5294,14 @@
       <c r="O24" s="10">
         <v>0</v>
       </c>
-      <c r="P24" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="8"/>
-    </row>
-    <row r="25" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P24" s="10"/>
+      <c r="Q24" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="8"/>
+    </row>
+    <row r="25" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -5257,24 +5338,25 @@
       <c r="L25" s="10">
         <v>0</v>
       </c>
-      <c r="M25" s="35">
-        <v>0</v>
-      </c>
-      <c r="N25" s="35">
-        <v>0</v>
-      </c>
-      <c r="O25" s="35">
-        <v>1</v>
-      </c>
-      <c r="P25" s="37">
+      <c r="M25" s="31">
+        <v>0</v>
+      </c>
+      <c r="N25" s="31">
+        <v>0</v>
+      </c>
+      <c r="O25" s="31">
+        <v>1</v>
+      </c>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="21">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="R25" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -5294,10 +5376,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="20">
         <v>1</v>
@@ -5318,15 +5400,16 @@
         <v>1</v>
       </c>
       <c r="O26" s="20">
-        <v>6</v>
-      </c>
-      <c r="P26" s="21">
-        <f>SUM(E26:O26)</f>
-        <v>14</v>
-      </c>
-      <c r="Q26" s="8"/>
-    </row>
-    <row r="27" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="21">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R26" s="8"/>
+    </row>
+    <row r="27" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -5342,8 +5425,8 @@
       <c r="E27" s="20">
         <v>1</v>
       </c>
-      <c r="F27" s="42">
-        <v>1</v>
+      <c r="F27" s="20">
+        <v>0</v>
       </c>
       <c r="G27" s="20">
         <v>0</v>
@@ -5372,14 +5455,18 @@
       <c r="O27" s="20">
         <v>0</v>
       </c>
-      <c r="P27" s="21">
+      <c r="P27" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="21">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -5423,15 +5510,16 @@
         <v>0</v>
       </c>
       <c r="O28" s="20">
-        <v>2</v>
-      </c>
-      <c r="P28" s="21">
-        <f>SUM(E28:O28)</f>
         <v>3</v>
       </c>
-      <c r="Q28" s="8"/>
-    </row>
-    <row r="29" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="41"/>
+      <c r="Q28" s="21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="R28" s="8"/>
+    </row>
+    <row r="29" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -5477,14 +5565,16 @@
       <c r="O29" s="20">
         <v>0</v>
       </c>
-      <c r="P29" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="s">
+      <c r="P29" s="41"/>
+      <c r="Q29" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -5504,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="20">
         <v>0</v>
@@ -5530,13 +5620,14 @@
       <c r="O30" s="20">
         <v>2</v>
       </c>
-      <c r="P30" s="21">
-        <f>SUM(E30:O30)</f>
-        <v>4</v>
-      </c>
-      <c r="Q30" s="8"/>
-    </row>
-    <row r="31" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P30" s="41"/>
+      <c r="Q30" s="21">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="R30" s="8"/>
+    </row>
+    <row r="31" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -5582,14 +5673,16 @@
       <c r="O31" s="20">
         <v>0</v>
       </c>
-      <c r="P31" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="8" t="s">
+      <c r="P31" s="41"/>
+      <c r="Q31" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
@@ -5635,13 +5728,14 @@
       <c r="O32" s="20">
         <v>2</v>
       </c>
-      <c r="P32" s="21">
-        <f>SUM(E32:O32)</f>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="21">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q32" s="8"/>
-    </row>
-    <row r="33" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R32" s="8"/>
+    </row>
+    <row r="33" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -5687,14 +5781,16 @@
       <c r="O33" s="20">
         <v>0</v>
       </c>
-      <c r="P33" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="8" t="s">
+      <c r="P33" s="41"/>
+      <c r="Q33" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>17</v>
       </c>
@@ -5717,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="20">
         <v>0</v>
@@ -5740,13 +5836,14 @@
       <c r="O34" s="20">
         <v>4</v>
       </c>
-      <c r="P34" s="21">
-        <f>SUM(E34:O34)</f>
-        <v>5</v>
-      </c>
-      <c r="Q34" s="8"/>
-    </row>
-    <row r="35" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P34" s="41"/>
+      <c r="Q34" s="21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="R34" s="8"/>
+    </row>
+    <row r="35" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
@@ -5792,14 +5889,16 @@
       <c r="O35" s="20">
         <v>0</v>
       </c>
-      <c r="P35" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="s">
+      <c r="P35" s="41"/>
+      <c r="Q35" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
@@ -5845,13 +5944,14 @@
       <c r="O36" s="5">
         <v>2</v>
       </c>
-      <c r="P36" s="43">
-        <f>SUM(E36:O36)</f>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="21">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q36" s="8"/>
-    </row>
-    <row r="37" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R36" s="8"/>
+    </row>
+    <row r="37" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>29</v>
       </c>
@@ -5864,47 +5964,49 @@
       <c r="D37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="36">
-        <v>0</v>
-      </c>
-      <c r="F37" s="36">
-        <v>0</v>
-      </c>
-      <c r="G37" s="36">
-        <v>0</v>
-      </c>
-      <c r="H37" s="36">
-        <v>0</v>
-      </c>
-      <c r="I37" s="36">
-        <v>0</v>
-      </c>
-      <c r="J37" s="36">
-        <v>0</v>
-      </c>
-      <c r="K37" s="36">
-        <v>0</v>
-      </c>
-      <c r="L37" s="36">
-        <v>0</v>
-      </c>
-      <c r="M37" s="36">
-        <v>0</v>
-      </c>
-      <c r="N37" s="36">
-        <v>0</v>
-      </c>
-      <c r="O37" s="36">
-        <v>0</v>
-      </c>
-      <c r="P37" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="8" t="s">
+      <c r="E37" s="32">
+        <v>0</v>
+      </c>
+      <c r="F37" s="32">
+        <v>0</v>
+      </c>
+      <c r="G37" s="32">
+        <v>0</v>
+      </c>
+      <c r="H37" s="32">
+        <v>0</v>
+      </c>
+      <c r="I37" s="32">
+        <v>0</v>
+      </c>
+      <c r="J37" s="32">
+        <v>0</v>
+      </c>
+      <c r="K37" s="32">
+        <v>0</v>
+      </c>
+      <c r="L37" s="32">
+        <v>0</v>
+      </c>
+      <c r="M37" s="32">
+        <v>0</v>
+      </c>
+      <c r="N37" s="32">
+        <v>0</v>
+      </c>
+      <c r="O37" s="32">
+        <v>0</v>
+      </c>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
@@ -5948,15 +6050,16 @@
         <v>0</v>
       </c>
       <c r="O38" s="20">
-        <v>1</v>
-      </c>
-      <c r="P38" s="21">
-        <f>SUM(E38:O38)</f>
-        <v>5</v>
-      </c>
-      <c r="Q38" s="8"/>
-    </row>
-    <row r="39" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="R38" s="8"/>
+    </row>
+    <row r="39" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>29</v>
       </c>
@@ -5969,47 +6072,49 @@
       <c r="D39" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="36">
-        <v>0</v>
-      </c>
-      <c r="F39" s="36">
-        <v>0</v>
-      </c>
-      <c r="G39" s="36">
-        <v>0</v>
-      </c>
-      <c r="H39" s="36">
-        <v>0</v>
-      </c>
-      <c r="I39" s="36">
-        <v>0</v>
-      </c>
-      <c r="J39" s="36">
-        <v>0</v>
-      </c>
-      <c r="K39" s="36">
-        <v>0</v>
-      </c>
-      <c r="L39" s="36">
-        <v>0</v>
-      </c>
-      <c r="M39" s="36">
-        <v>0</v>
-      </c>
-      <c r="N39" s="36">
-        <v>0</v>
-      </c>
-      <c r="O39" s="36">
-        <v>0</v>
-      </c>
-      <c r="P39" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="8" t="s">
+      <c r="E39" s="32">
+        <v>0</v>
+      </c>
+      <c r="F39" s="32">
+        <v>0</v>
+      </c>
+      <c r="G39" s="32">
+        <v>0</v>
+      </c>
+      <c r="H39" s="32">
+        <v>0</v>
+      </c>
+      <c r="I39" s="32">
+        <v>0</v>
+      </c>
+      <c r="J39" s="32">
+        <v>0</v>
+      </c>
+      <c r="K39" s="32">
+        <v>0</v>
+      </c>
+      <c r="L39" s="32">
+        <v>0</v>
+      </c>
+      <c r="M39" s="32">
+        <v>0</v>
+      </c>
+      <c r="N39" s="32">
+        <v>0</v>
+      </c>
+      <c r="O39" s="32">
+        <v>0</v>
+      </c>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R39" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>29</v>
       </c>
@@ -6055,13 +6160,14 @@
       <c r="O40" s="20">
         <v>2</v>
       </c>
-      <c r="P40" s="21">
-        <f>SUM(E40:O40)</f>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="21">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q40" s="8"/>
-    </row>
-    <row r="41" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R40" s="8"/>
+    </row>
+    <row r="41" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>29</v>
       </c>
@@ -6074,47 +6180,49 @@
       <c r="D41" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="36">
-        <v>0</v>
-      </c>
-      <c r="F41" s="36">
-        <v>0</v>
-      </c>
-      <c r="G41" s="36">
-        <v>0</v>
-      </c>
-      <c r="H41" s="36">
-        <v>0</v>
-      </c>
-      <c r="I41" s="36">
-        <v>0</v>
-      </c>
-      <c r="J41" s="36">
-        <v>0</v>
-      </c>
-      <c r="K41" s="36">
-        <v>0</v>
-      </c>
-      <c r="L41" s="36">
-        <v>0</v>
-      </c>
-      <c r="M41" s="36">
-        <v>0</v>
-      </c>
-      <c r="N41" s="36">
-        <v>0</v>
-      </c>
-      <c r="O41" s="36">
-        <v>0</v>
-      </c>
-      <c r="P41" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="8" t="s">
+      <c r="E41" s="32">
+        <v>0</v>
+      </c>
+      <c r="F41" s="32">
+        <v>0</v>
+      </c>
+      <c r="G41" s="32">
+        <v>0</v>
+      </c>
+      <c r="H41" s="32">
+        <v>0</v>
+      </c>
+      <c r="I41" s="32">
+        <v>0</v>
+      </c>
+      <c r="J41" s="32">
+        <v>0</v>
+      </c>
+      <c r="K41" s="32">
+        <v>0</v>
+      </c>
+      <c r="L41" s="32">
+        <v>0</v>
+      </c>
+      <c r="M41" s="32">
+        <v>0</v>
+      </c>
+      <c r="N41" s="32">
+        <v>0</v>
+      </c>
+      <c r="O41" s="32">
+        <v>0</v>
+      </c>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>29</v>
       </c>
@@ -6158,15 +6266,16 @@
         <v>1</v>
       </c>
       <c r="O42" s="20">
-        <v>5</v>
-      </c>
-      <c r="P42" s="21">
-        <f>SUM(E42:O42)</f>
-        <v>11</v>
-      </c>
-      <c r="Q42" s="8"/>
-    </row>
-    <row r="43" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="21">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="R42" s="8"/>
+    </row>
+    <row r="43" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>29</v>
       </c>
@@ -6179,47 +6288,49 @@
       <c r="D43" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="36">
-        <v>0</v>
-      </c>
-      <c r="F43" s="36">
-        <v>0</v>
-      </c>
-      <c r="G43" s="36">
-        <v>0</v>
-      </c>
-      <c r="H43" s="36">
-        <v>0</v>
-      </c>
-      <c r="I43" s="36">
-        <v>0</v>
-      </c>
-      <c r="J43" s="36">
-        <v>0</v>
-      </c>
-      <c r="K43" s="36">
-        <v>0</v>
-      </c>
-      <c r="L43" s="36">
-        <v>0</v>
-      </c>
-      <c r="M43" s="36">
-        <v>0</v>
-      </c>
-      <c r="N43" s="36">
-        <v>0</v>
-      </c>
-      <c r="O43" s="36">
-        <v>0</v>
-      </c>
-      <c r="P43" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="8" t="s">
+      <c r="E43" s="32">
+        <v>0</v>
+      </c>
+      <c r="F43" s="32">
+        <v>0</v>
+      </c>
+      <c r="G43" s="32">
+        <v>0</v>
+      </c>
+      <c r="H43" s="32">
+        <v>0</v>
+      </c>
+      <c r="I43" s="32">
+        <v>0</v>
+      </c>
+      <c r="J43" s="32">
+        <v>0</v>
+      </c>
+      <c r="K43" s="32">
+        <v>0</v>
+      </c>
+      <c r="L43" s="32">
+        <v>0</v>
+      </c>
+      <c r="M43" s="32">
+        <v>0</v>
+      </c>
+      <c r="N43" s="32">
+        <v>0</v>
+      </c>
+      <c r="O43" s="32">
+        <v>0</v>
+      </c>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>30</v>
       </c>
@@ -6232,46 +6343,47 @@
       <c r="D44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E44" s="36">
-        <v>0</v>
-      </c>
-      <c r="F44" s="36">
-        <v>0</v>
-      </c>
-      <c r="G44" s="36">
-        <v>0</v>
-      </c>
-      <c r="H44" s="36">
-        <v>0</v>
-      </c>
-      <c r="I44" s="36">
-        <v>0</v>
-      </c>
-      <c r="J44" s="36">
-        <v>0</v>
-      </c>
-      <c r="K44" s="36">
-        <v>0</v>
-      </c>
-      <c r="L44" s="36">
-        <v>1</v>
-      </c>
-      <c r="M44" s="36">
-        <v>0</v>
-      </c>
-      <c r="N44" s="36">
-        <v>0</v>
-      </c>
-      <c r="O44" s="36">
+      <c r="E44" s="32">
+        <v>0</v>
+      </c>
+      <c r="F44" s="32">
+        <v>0</v>
+      </c>
+      <c r="G44" s="32">
+        <v>0</v>
+      </c>
+      <c r="H44" s="32">
+        <v>0</v>
+      </c>
+      <c r="I44" s="32">
+        <v>0</v>
+      </c>
+      <c r="J44" s="32">
+        <v>0</v>
+      </c>
+      <c r="K44" s="32">
+        <v>0</v>
+      </c>
+      <c r="L44" s="32">
+        <v>1</v>
+      </c>
+      <c r="M44" s="32">
+        <v>0</v>
+      </c>
+      <c r="N44" s="32">
+        <v>0</v>
+      </c>
+      <c r="O44" s="32">
         <v>3</v>
       </c>
-      <c r="P44" s="37">
-        <f t="shared" ref="P44:P49" si="1">SUM(E44:O44)</f>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="21">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Q44" s="8"/>
-    </row>
-    <row r="45" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="R44" s="8"/>
+    </row>
+    <row r="45" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>30</v>
       </c>
@@ -6284,48 +6396,49 @@
       <c r="D45" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="36">
-        <v>1</v>
-      </c>
-      <c r="F45" s="36">
-        <v>0</v>
-      </c>
-      <c r="G45" s="36">
-        <v>0</v>
-      </c>
-      <c r="H45" s="36">
-        <v>0</v>
-      </c>
-      <c r="I45" s="36">
-        <v>0</v>
-      </c>
-      <c r="J45" s="36">
-        <v>0</v>
-      </c>
-      <c r="K45" s="36">
-        <v>0</v>
-      </c>
-      <c r="L45" s="36">
-        <v>0</v>
-      </c>
-      <c r="M45" s="36">
-        <v>0</v>
-      </c>
-      <c r="N45" s="36">
-        <v>0</v>
-      </c>
-      <c r="O45" s="36">
-        <v>0</v>
-      </c>
-      <c r="P45" s="37">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q45" s="8" t="s">
+      <c r="E45" s="32">
+        <v>1</v>
+      </c>
+      <c r="F45" s="32">
+        <v>0</v>
+      </c>
+      <c r="G45" s="32">
+        <v>0</v>
+      </c>
+      <c r="H45" s="32">
+        <v>0</v>
+      </c>
+      <c r="I45" s="32">
+        <v>0</v>
+      </c>
+      <c r="J45" s="32">
+        <v>0</v>
+      </c>
+      <c r="K45" s="32">
+        <v>0</v>
+      </c>
+      <c r="L45" s="32">
+        <v>0</v>
+      </c>
+      <c r="M45" s="32">
+        <v>0</v>
+      </c>
+      <c r="N45" s="32">
+        <v>0</v>
+      </c>
+      <c r="O45" s="32">
+        <v>0</v>
+      </c>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R45" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
@@ -6338,46 +6451,47 @@
       <c r="D46" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="38">
-        <v>1</v>
-      </c>
-      <c r="F46" s="38">
-        <v>2</v>
-      </c>
-      <c r="G46" s="38">
-        <v>0</v>
-      </c>
-      <c r="H46" s="38">
-        <v>0</v>
-      </c>
-      <c r="I46" s="38">
-        <v>1</v>
-      </c>
-      <c r="J46" s="38">
-        <v>0</v>
-      </c>
-      <c r="K46" s="38">
-        <v>0</v>
-      </c>
-      <c r="L46" s="38">
-        <v>0</v>
-      </c>
-      <c r="M46" s="38">
-        <v>0</v>
-      </c>
-      <c r="N46" s="38">
-        <v>0</v>
-      </c>
-      <c r="O46" s="38">
-        <v>2</v>
-      </c>
-      <c r="P46" s="37">
-        <f t="shared" si="1"/>
+      <c r="E46" s="33">
+        <v>1</v>
+      </c>
+      <c r="F46" s="33">
+        <v>2</v>
+      </c>
+      <c r="G46" s="33">
+        <v>0</v>
+      </c>
+      <c r="H46" s="33">
+        <v>0</v>
+      </c>
+      <c r="I46" s="33">
+        <v>1</v>
+      </c>
+      <c r="J46" s="33">
+        <v>0</v>
+      </c>
+      <c r="K46" s="33">
+        <v>0</v>
+      </c>
+      <c r="L46" s="33">
+        <v>0</v>
+      </c>
+      <c r="M46" s="33">
+        <v>0</v>
+      </c>
+      <c r="N46" s="33">
+        <v>0</v>
+      </c>
+      <c r="O46" s="33">
+        <v>2</v>
+      </c>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="21">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Q46" s="8"/>
-    </row>
-    <row r="47" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="R46" s="8"/>
+    </row>
+    <row r="47" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>30</v>
       </c>
@@ -6390,48 +6504,49 @@
       <c r="D47" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E47" s="39">
-        <v>0</v>
-      </c>
-      <c r="F47" s="39">
-        <v>0</v>
-      </c>
-      <c r="G47" s="39">
-        <v>0</v>
-      </c>
-      <c r="H47" s="39">
-        <v>0</v>
-      </c>
-      <c r="I47" s="39">
-        <v>0</v>
-      </c>
-      <c r="J47" s="39">
-        <v>0</v>
-      </c>
-      <c r="K47" s="39">
-        <v>0</v>
-      </c>
-      <c r="L47" s="39">
-        <v>1</v>
-      </c>
-      <c r="M47" s="39">
-        <v>0</v>
-      </c>
-      <c r="N47" s="39">
-        <v>0</v>
-      </c>
-      <c r="O47" s="40">
-        <v>0</v>
-      </c>
-      <c r="P47" s="37">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q47" s="8" t="s">
+      <c r="E47" s="15">
+        <v>0</v>
+      </c>
+      <c r="F47" s="15">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0</v>
+      </c>
+      <c r="H47" s="15">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
+        <v>0</v>
+      </c>
+      <c r="J47" s="15">
+        <v>0</v>
+      </c>
+      <c r="K47" s="15">
+        <v>0</v>
+      </c>
+      <c r="L47" s="15">
+        <v>1</v>
+      </c>
+      <c r="M47" s="15">
+        <v>0</v>
+      </c>
+      <c r="N47" s="15">
+        <v>0</v>
+      </c>
+      <c r="O47" s="15">
+        <v>0</v>
+      </c>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R47" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>30</v>
       </c>
@@ -6444,46 +6559,47 @@
       <c r="D48" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="38">
-        <v>1</v>
-      </c>
-      <c r="F48" s="38">
-        <v>1</v>
-      </c>
-      <c r="G48" s="38">
-        <v>0</v>
-      </c>
-      <c r="H48" s="38">
-        <v>0</v>
-      </c>
-      <c r="I48" s="38">
-        <v>0</v>
-      </c>
-      <c r="J48" s="38">
-        <v>0</v>
-      </c>
-      <c r="K48" s="38">
-        <v>0</v>
-      </c>
-      <c r="L48" s="38">
-        <v>2</v>
-      </c>
-      <c r="M48" s="38">
-        <v>0</v>
-      </c>
-      <c r="N48" s="38">
-        <v>0</v>
-      </c>
-      <c r="O48" s="38">
+      <c r="E48" s="33">
+        <v>1</v>
+      </c>
+      <c r="F48" s="33">
+        <v>1</v>
+      </c>
+      <c r="G48" s="33">
+        <v>0</v>
+      </c>
+      <c r="H48" s="33">
+        <v>0</v>
+      </c>
+      <c r="I48" s="33">
+        <v>0</v>
+      </c>
+      <c r="J48" s="33">
+        <v>0</v>
+      </c>
+      <c r="K48" s="33">
+        <v>0</v>
+      </c>
+      <c r="L48" s="33">
+        <v>2</v>
+      </c>
+      <c r="M48" s="33">
+        <v>0</v>
+      </c>
+      <c r="N48" s="33">
+        <v>0</v>
+      </c>
+      <c r="O48" s="33">
         <v>4</v>
       </c>
-      <c r="P48" s="37">
-        <f t="shared" si="1"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="21">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="Q48" s="8"/>
-    </row>
-    <row r="49" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="R48" s="8"/>
+    </row>
+    <row r="49" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>30</v>
       </c>
@@ -6529,15 +6645,16 @@
       <c r="O49" s="10">
         <v>0</v>
       </c>
-      <c r="P49" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="8" t="s">
+      <c r="P49" s="10"/>
+      <c r="Q49" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R49" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -6581,14 +6698,16 @@
         <v>0</v>
       </c>
       <c r="O50" s="20">
-        <v>58</v>
-      </c>
-      <c r="P50" s="7">
-        <v>69</v>
-      </c>
-      <c r="Q50" s="8"/>
-    </row>
-    <row r="51" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="21">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="R50" s="8"/>
+    </row>
+    <row r="51" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>17</v>
       </c>
@@ -6632,14 +6751,16 @@
         <v>0</v>
       </c>
       <c r="O51" s="20">
-        <v>51</v>
-      </c>
-      <c r="P51" s="7">
-        <v>61</v>
-      </c>
-      <c r="Q51" s="8"/>
-    </row>
-    <row r="52" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="21">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="R51" s="8"/>
+    </row>
+    <row r="52" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>17</v>
       </c>
@@ -6683,14 +6804,16 @@
         <v>0</v>
       </c>
       <c r="O52" s="20">
-        <v>62</v>
-      </c>
-      <c r="P52" s="7">
-        <v>69</v>
-      </c>
-      <c r="Q52" s="8"/>
-    </row>
-    <row r="53" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="21">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="R52" s="8"/>
+    </row>
+    <row r="53" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>17</v>
       </c>
@@ -6704,10 +6827,10 @@
         <v>38</v>
       </c>
       <c r="E53" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="20">
         <v>2</v>
@@ -6716,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" s="20">
         <v>0</v>
@@ -6734,14 +6857,16 @@
         <v>0</v>
       </c>
       <c r="O53" s="20">
-        <v>56</v>
-      </c>
-      <c r="P53" s="7">
-        <v>67</v>
-      </c>
-      <c r="Q53" s="8"/>
-    </row>
-    <row r="54" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="21">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="R53" s="8"/>
+    </row>
+    <row r="54" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>17</v>
       </c>
@@ -6755,7 +6880,7 @@
         <v>38</v>
       </c>
       <c r="E54" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="20">
         <v>1</v>
@@ -6767,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="20">
         <v>0</v>
@@ -6785,14 +6910,16 @@
         <v>0</v>
       </c>
       <c r="O54" s="20">
-        <v>54</v>
-      </c>
-      <c r="P54" s="7">
-        <v>60</v>
-      </c>
-      <c r="Q54" s="8"/>
-    </row>
-    <row r="55" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="21">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="R54" s="8"/>
+    </row>
+    <row r="55" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
@@ -6838,12 +6965,14 @@
       <c r="O55" s="20">
         <v>80</v>
       </c>
-      <c r="P55" s="7">
+      <c r="P55" s="20"/>
+      <c r="Q55" s="21">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="Q55" s="8"/>
-    </row>
-    <row r="56" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R55" s="8"/>
+    </row>
+    <row r="56" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
@@ -6889,12 +7018,14 @@
       <c r="O56" s="20">
         <v>89</v>
       </c>
-      <c r="P56" s="7">
+      <c r="P56" s="20"/>
+      <c r="Q56" s="21">
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="Q56" s="8"/>
-    </row>
-    <row r="57" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R56" s="8"/>
+    </row>
+    <row r="57" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
@@ -6940,12 +7071,14 @@
       <c r="O57" s="20">
         <v>68</v>
       </c>
-      <c r="P57" s="7">
+      <c r="P57" s="20"/>
+      <c r="Q57" s="21">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="Q57" s="8"/>
-    </row>
-    <row r="58" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R57" s="8"/>
+    </row>
+    <row r="58" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>29</v>
       </c>
@@ -6991,12 +7124,14 @@
       <c r="O58" s="20">
         <v>50</v>
       </c>
-      <c r="P58" s="7">
+      <c r="P58" s="20"/>
+      <c r="Q58" s="21">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="Q58" s="8"/>
-    </row>
-    <row r="59" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="R58" s="8"/>
+    </row>
+    <row r="59" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>30</v>
       </c>
@@ -7042,12 +7177,14 @@
       <c r="O59" s="22">
         <v>103</v>
       </c>
-      <c r="P59" s="7">
+      <c r="P59" s="22"/>
+      <c r="Q59" s="21">
+        <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="Q59" s="8"/>
-    </row>
-    <row r="60" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="R59" s="8"/>
+    </row>
+    <row r="60" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>30</v>
       </c>
@@ -7093,12 +7230,14 @@
       <c r="O60" s="20">
         <v>147</v>
       </c>
-      <c r="P60" s="7">
+      <c r="P60" s="20"/>
+      <c r="Q60" s="21">
+        <f t="shared" si="0"/>
         <v>158</v>
       </c>
-      <c r="Q60" s="8"/>
-    </row>
-    <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="R60" s="8"/>
+    </row>
+    <row r="61" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>30</v>
       </c>
@@ -7144,12 +7283,14 @@
       <c r="O61" s="11">
         <v>106</v>
       </c>
-      <c r="P61" s="7">
+      <c r="P61" s="11"/>
+      <c r="Q61" s="21">
+        <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="Q61" s="8"/>
-    </row>
-    <row r="62" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R61" s="8"/>
+    </row>
+    <row r="62" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>17</v>
       </c>
@@ -7162,46 +7303,47 @@
       <c r="D62" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="30">
         <v>10</v>
       </c>
-      <c r="F62" s="33">
-        <v>1</v>
-      </c>
-      <c r="G62" s="33">
-        <v>2</v>
-      </c>
-      <c r="H62" s="33">
-        <v>1</v>
-      </c>
-      <c r="I62" s="33">
-        <v>1</v>
-      </c>
-      <c r="J62" s="33">
+      <c r="F62" s="30">
+        <v>1</v>
+      </c>
+      <c r="G62" s="30">
+        <v>2</v>
+      </c>
+      <c r="H62" s="30">
+        <v>1</v>
+      </c>
+      <c r="I62" s="30">
+        <v>1</v>
+      </c>
+      <c r="J62" s="30">
         <v>4</v>
       </c>
-      <c r="K62" s="33">
-        <v>2</v>
-      </c>
-      <c r="L62" s="33">
+      <c r="K62" s="30">
+        <v>2</v>
+      </c>
+      <c r="L62" s="30">
         <v>9</v>
       </c>
-      <c r="M62" s="33">
-        <v>1</v>
-      </c>
-      <c r="N62" s="33">
-        <v>0</v>
-      </c>
-      <c r="O62" s="33">
+      <c r="M62" s="30">
+        <v>1</v>
+      </c>
+      <c r="N62" s="30">
+        <v>0</v>
+      </c>
+      <c r="O62" s="30">
         <v>32</v>
       </c>
-      <c r="P62" s="34">
-        <f>SUM(E62:O62)</f>
+      <c r="P62" s="42"/>
+      <c r="Q62" s="21">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="Q62" s="8"/>
-    </row>
-    <row r="63" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R62" s="8"/>
+    </row>
+    <row r="63" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -7214,48 +7356,49 @@
       <c r="D63" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="30">
         <v>6</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="30">
         <v>3</v>
       </c>
-      <c r="G63" s="33">
-        <v>1</v>
-      </c>
-      <c r="H63" s="33">
-        <v>0</v>
-      </c>
-      <c r="I63" s="33">
-        <v>2</v>
-      </c>
-      <c r="J63" s="33">
-        <v>0</v>
-      </c>
-      <c r="K63" s="33">
-        <v>0</v>
-      </c>
-      <c r="L63" s="33">
+      <c r="G63" s="30">
+        <v>1</v>
+      </c>
+      <c r="H63" s="30">
+        <v>0</v>
+      </c>
+      <c r="I63" s="30">
+        <v>2</v>
+      </c>
+      <c r="J63" s="30">
+        <v>0</v>
+      </c>
+      <c r="K63" s="30">
+        <v>0</v>
+      </c>
+      <c r="L63" s="30">
         <v>12</v>
       </c>
-      <c r="M63" s="33">
-        <v>4</v>
-      </c>
-      <c r="N63" s="33">
-        <v>1</v>
-      </c>
-      <c r="O63" s="33">
+      <c r="M63" s="30">
+        <v>3</v>
+      </c>
+      <c r="N63" s="30">
+        <v>1</v>
+      </c>
+      <c r="O63" s="30">
         <v>10</v>
       </c>
-      <c r="P63" s="34">
-        <f t="shared" ref="P63:P64" si="2">SUM(E63:O63)</f>
-        <v>39</v>
-      </c>
-      <c r="Q63" s="8" t="s">
+      <c r="P63" s="42"/>
+      <c r="Q63" s="21">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="R63" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>17</v>
       </c>
@@ -7268,46 +7411,47 @@
       <c r="D64" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="33">
-        <v>9</v>
-      </c>
-      <c r="F64" s="33">
-        <v>2</v>
-      </c>
-      <c r="G64" s="33">
-        <v>3</v>
-      </c>
-      <c r="H64" s="33">
-        <v>2</v>
-      </c>
-      <c r="I64" s="33">
-        <v>1</v>
-      </c>
-      <c r="J64" s="33">
-        <v>1</v>
-      </c>
-      <c r="K64" s="33">
-        <v>2</v>
-      </c>
-      <c r="L64" s="33">
-        <v>14</v>
-      </c>
-      <c r="M64" s="33">
-        <v>1</v>
-      </c>
-      <c r="N64" s="33">
-        <v>0</v>
-      </c>
-      <c r="O64" s="33">
-        <v>33</v>
-      </c>
-      <c r="P64" s="34">
-        <f t="shared" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="Q64" s="8"/>
-    </row>
-    <row r="65" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="30">
+        <v>4</v>
+      </c>
+      <c r="F64" s="30">
+        <v>2</v>
+      </c>
+      <c r="G64" s="30">
+        <v>2</v>
+      </c>
+      <c r="H64" s="30">
+        <v>2</v>
+      </c>
+      <c r="I64" s="30">
+        <v>0</v>
+      </c>
+      <c r="J64" s="30">
+        <v>1</v>
+      </c>
+      <c r="K64" s="30">
+        <v>2</v>
+      </c>
+      <c r="L64" s="30">
+        <v>13</v>
+      </c>
+      <c r="M64" s="30">
+        <v>1</v>
+      </c>
+      <c r="N64" s="30">
+        <v>0</v>
+      </c>
+      <c r="O64" s="30">
+        <v>24</v>
+      </c>
+      <c r="P64" s="42"/>
+      <c r="Q64" s="21">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="R64" s="8"/>
+    </row>
+    <row r="65" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>17</v>
       </c>
@@ -7320,48 +7464,49 @@
       <c r="D65" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="33">
-        <v>4</v>
-      </c>
-      <c r="F65" s="33">
-        <v>2</v>
-      </c>
-      <c r="G65" s="33">
-        <v>0</v>
-      </c>
-      <c r="H65" s="33">
-        <v>1</v>
-      </c>
-      <c r="I65" s="33">
-        <v>1</v>
-      </c>
-      <c r="J65" s="33">
-        <v>1</v>
-      </c>
-      <c r="K65" s="33">
-        <v>0</v>
-      </c>
-      <c r="L65" s="33">
+      <c r="E65" s="30">
         <v>3</v>
       </c>
-      <c r="M65" s="33">
+      <c r="F65" s="30">
+        <v>2</v>
+      </c>
+      <c r="G65" s="30">
+        <v>0</v>
+      </c>
+      <c r="H65" s="30">
+        <v>1</v>
+      </c>
+      <c r="I65" s="30">
+        <v>1</v>
+      </c>
+      <c r="J65" s="30">
+        <v>0</v>
+      </c>
+      <c r="K65" s="30">
+        <v>0</v>
+      </c>
+      <c r="L65" s="30">
         <v>3</v>
       </c>
-      <c r="N65" s="33">
-        <v>0</v>
-      </c>
-      <c r="O65" s="33">
+      <c r="M65" s="30">
+        <v>3</v>
+      </c>
+      <c r="N65" s="30">
+        <v>0</v>
+      </c>
+      <c r="O65" s="30">
         <v>9</v>
       </c>
-      <c r="P65" s="34">
-        <f t="shared" ref="P65:P66" si="3">SUM(E65:O65)</f>
-        <v>24</v>
-      </c>
-      <c r="Q65" s="8" t="s">
+      <c r="P65" s="42"/>
+      <c r="Q65" s="21">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="R65" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>17</v>
       </c>
@@ -7374,46 +7519,47 @@
       <c r="D66" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="30">
+        <v>7</v>
+      </c>
+      <c r="F66" s="30">
+        <v>4</v>
+      </c>
+      <c r="G66" s="30">
+        <v>0</v>
+      </c>
+      <c r="H66" s="30">
+        <v>0</v>
+      </c>
+      <c r="I66" s="30">
+        <v>1</v>
+      </c>
+      <c r="J66" s="30">
+        <v>1</v>
+      </c>
+      <c r="K66" s="30">
+        <v>2</v>
+      </c>
+      <c r="L66" s="30">
         <v>9</v>
       </c>
-      <c r="F66" s="33">
-        <v>4</v>
-      </c>
-      <c r="G66" s="33">
-        <v>0</v>
-      </c>
-      <c r="H66" s="33">
-        <v>0</v>
-      </c>
-      <c r="I66" s="33">
-        <v>1</v>
-      </c>
-      <c r="J66" s="33">
-        <v>1</v>
-      </c>
-      <c r="K66" s="33">
-        <v>2</v>
-      </c>
-      <c r="L66" s="33">
-        <v>9</v>
-      </c>
-      <c r="M66" s="33">
-        <v>2</v>
-      </c>
-      <c r="N66" s="33">
-        <v>0</v>
-      </c>
-      <c r="O66" s="33">
-        <v>20</v>
-      </c>
-      <c r="P66" s="34">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="Q66" s="8"/>
-    </row>
-    <row r="67" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="30">
+        <v>2</v>
+      </c>
+      <c r="N66" s="30">
+        <v>0</v>
+      </c>
+      <c r="O66" s="30">
+        <v>10</v>
+      </c>
+      <c r="P66" s="42"/>
+      <c r="Q66" s="21">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="R66" s="8"/>
+    </row>
+    <row r="67" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -7426,48 +7572,49 @@
       <c r="D67" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E67" s="33">
-        <v>6</v>
-      </c>
-      <c r="F67" s="33">
-        <v>1</v>
-      </c>
-      <c r="G67" s="33">
-        <v>2</v>
-      </c>
-      <c r="H67" s="33">
-        <v>1</v>
-      </c>
-      <c r="I67" s="33">
-        <v>1</v>
-      </c>
-      <c r="J67" s="33">
-        <v>1</v>
-      </c>
-      <c r="K67" s="33">
-        <v>0</v>
-      </c>
-      <c r="L67" s="33">
+      <c r="E67" s="30">
+        <v>5</v>
+      </c>
+      <c r="F67" s="30">
+        <v>1</v>
+      </c>
+      <c r="G67" s="30">
+        <v>1</v>
+      </c>
+      <c r="H67" s="30">
+        <v>1</v>
+      </c>
+      <c r="I67" s="30">
+        <v>1</v>
+      </c>
+      <c r="J67" s="30">
+        <v>1</v>
+      </c>
+      <c r="K67" s="30">
+        <v>0</v>
+      </c>
+      <c r="L67" s="30">
         <v>12</v>
       </c>
-      <c r="M67" s="33">
+      <c r="M67" s="30">
         <v>5</v>
       </c>
-      <c r="N67" s="33">
+      <c r="N67" s="30">
         <v>3</v>
       </c>
-      <c r="O67" s="33">
+      <c r="O67" s="30">
         <v>13</v>
       </c>
-      <c r="P67" s="34">
-        <f t="shared" ref="P67:P68" si="4">SUM(E67:O67)</f>
-        <v>45</v>
-      </c>
-      <c r="Q67" s="8" t="s">
+      <c r="P67" s="42"/>
+      <c r="Q67" s="21">
+        <f t="shared" ref="Q67:Q85" si="1">SUM(E67:P67)</f>
+        <v>43</v>
+      </c>
+      <c r="R67" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>17</v>
       </c>
@@ -7480,46 +7627,47 @@
       <c r="D68" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="30">
+        <v>4</v>
+      </c>
+      <c r="F68" s="30">
+        <v>1</v>
+      </c>
+      <c r="G68" s="30">
+        <v>2</v>
+      </c>
+      <c r="H68" s="30">
+        <v>0</v>
+      </c>
+      <c r="I68" s="30">
+        <v>0</v>
+      </c>
+      <c r="J68" s="30">
+        <v>0</v>
+      </c>
+      <c r="K68" s="30">
+        <v>2</v>
+      </c>
+      <c r="L68" s="30">
+        <v>5</v>
+      </c>
+      <c r="M68" s="30">
+        <v>0</v>
+      </c>
+      <c r="N68" s="30">
+        <v>0</v>
+      </c>
+      <c r="O68" s="30">
         <v>7</v>
       </c>
-      <c r="F68" s="33">
-        <v>2</v>
-      </c>
-      <c r="G68" s="33">
-        <v>3</v>
-      </c>
-      <c r="H68" s="33">
-        <v>1</v>
-      </c>
-      <c r="I68" s="33">
-        <v>0</v>
-      </c>
-      <c r="J68" s="33">
-        <v>1</v>
-      </c>
-      <c r="K68" s="33">
-        <v>2</v>
-      </c>
-      <c r="L68" s="33">
-        <v>6</v>
-      </c>
-      <c r="M68" s="33">
-        <v>0</v>
-      </c>
-      <c r="N68" s="33">
-        <v>0</v>
-      </c>
-      <c r="O68" s="33">
-        <v>20</v>
-      </c>
-      <c r="P68" s="34">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="Q68" s="8"/>
-    </row>
-    <row r="69" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P68" s="42"/>
+      <c r="Q68" s="21">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="R68" s="8"/>
+    </row>
+    <row r="69" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>17</v>
       </c>
@@ -7532,48 +7680,49 @@
       <c r="D69" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="30">
         <v>6</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="30">
         <v>3</v>
       </c>
-      <c r="G69" s="33">
-        <v>0</v>
-      </c>
-      <c r="H69" s="33">
-        <v>1</v>
-      </c>
-      <c r="I69" s="33">
-        <v>1</v>
-      </c>
-      <c r="J69" s="33">
-        <v>2</v>
-      </c>
-      <c r="K69" s="33">
-        <v>0</v>
-      </c>
-      <c r="L69" s="33">
-        <v>12</v>
-      </c>
-      <c r="M69" s="33">
+      <c r="G69" s="30">
+        <v>0</v>
+      </c>
+      <c r="H69" s="30">
+        <v>1</v>
+      </c>
+      <c r="I69" s="30">
+        <v>1</v>
+      </c>
+      <c r="J69" s="30">
+        <v>2</v>
+      </c>
+      <c r="K69" s="30">
+        <v>0</v>
+      </c>
+      <c r="L69" s="30">
+        <v>15</v>
+      </c>
+      <c r="M69" s="30">
         <v>5</v>
       </c>
-      <c r="N69" s="33">
-        <v>2</v>
-      </c>
-      <c r="O69" s="33">
-        <v>17</v>
-      </c>
-      <c r="P69" s="34">
-        <f t="shared" ref="P69:P70" si="5">SUM(E69:O69)</f>
-        <v>49</v>
-      </c>
-      <c r="Q69" s="8" t="s">
+      <c r="N69" s="30">
+        <v>2</v>
+      </c>
+      <c r="O69" s="30">
+        <v>16</v>
+      </c>
+      <c r="P69" s="42"/>
+      <c r="Q69" s="21">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="R69" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>17</v>
       </c>
@@ -7586,46 +7735,47 @@
       <c r="D70" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E70" s="33">
-        <v>6</v>
-      </c>
-      <c r="F70" s="33">
+      <c r="E70" s="30">
+        <v>5</v>
+      </c>
+      <c r="F70" s="30">
+        <v>3</v>
+      </c>
+      <c r="G70" s="30">
         <v>4</v>
       </c>
-      <c r="G70" s="33">
-        <v>3</v>
-      </c>
-      <c r="H70" s="33">
-        <v>1</v>
-      </c>
-      <c r="I70" s="33">
-        <v>1</v>
-      </c>
-      <c r="J70" s="33">
-        <v>2</v>
-      </c>
-      <c r="K70" s="33">
-        <v>1</v>
-      </c>
-      <c r="L70" s="33">
-        <v>9</v>
-      </c>
-      <c r="M70" s="33">
-        <v>0</v>
-      </c>
-      <c r="N70" s="33">
-        <v>0</v>
-      </c>
-      <c r="O70" s="33">
-        <v>25</v>
-      </c>
-      <c r="P70" s="34">
-        <f t="shared" si="5"/>
-        <v>52</v>
-      </c>
-      <c r="Q70" s="8"/>
-    </row>
-    <row r="71" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H70" s="30">
+        <v>1</v>
+      </c>
+      <c r="I70" s="30">
+        <v>1</v>
+      </c>
+      <c r="J70" s="30">
+        <v>2</v>
+      </c>
+      <c r="K70" s="30">
+        <v>1</v>
+      </c>
+      <c r="L70" s="30">
+        <v>10</v>
+      </c>
+      <c r="M70" s="30">
+        <v>0</v>
+      </c>
+      <c r="N70" s="30">
+        <v>0</v>
+      </c>
+      <c r="O70" s="30">
+        <v>22</v>
+      </c>
+      <c r="P70" s="42"/>
+      <c r="Q70" s="21">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="R70" s="8"/>
+    </row>
+    <row r="71" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>17</v>
       </c>
@@ -7638,48 +7788,49 @@
       <c r="D71" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="30">
         <v>5</v>
       </c>
-      <c r="F71" s="33">
-        <v>0</v>
-      </c>
-      <c r="G71" s="33">
-        <v>0</v>
-      </c>
-      <c r="H71" s="33">
-        <v>0</v>
-      </c>
-      <c r="I71" s="33">
-        <v>1</v>
-      </c>
-      <c r="J71" s="33">
-        <v>1</v>
-      </c>
-      <c r="K71" s="33">
-        <v>0</v>
-      </c>
-      <c r="L71" s="33">
-        <v>8</v>
-      </c>
-      <c r="M71" s="33">
+      <c r="F71" s="30">
+        <v>0</v>
+      </c>
+      <c r="G71" s="30">
+        <v>0</v>
+      </c>
+      <c r="H71" s="30">
+        <v>0</v>
+      </c>
+      <c r="I71" s="30">
+        <v>1</v>
+      </c>
+      <c r="J71" s="30">
+        <v>1</v>
+      </c>
+      <c r="K71" s="30">
+        <v>0</v>
+      </c>
+      <c r="L71" s="30">
+        <v>7</v>
+      </c>
+      <c r="M71" s="30">
         <v>4</v>
       </c>
-      <c r="N71" s="33">
+      <c r="N71" s="30">
         <v>3</v>
       </c>
-      <c r="O71" s="33">
+      <c r="O71" s="30">
         <v>5</v>
       </c>
-      <c r="P71" s="34">
-        <f t="shared" ref="P71:P73" si="6">SUM(E71:O71)</f>
-        <v>27</v>
-      </c>
-      <c r="Q71" s="8" t="s">
+      <c r="P71" s="42"/>
+      <c r="Q71" s="21">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="R71" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>29</v>
       </c>
@@ -7702,7 +7853,7 @@
         <v>3</v>
       </c>
       <c r="H72" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="20">
         <v>2</v>
@@ -7714,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M72" s="20">
         <v>0</v>
@@ -7723,15 +7874,16 @@
         <v>0</v>
       </c>
       <c r="O72" s="20">
-        <v>48</v>
-      </c>
-      <c r="P72" s="21">
-        <f t="shared" si="6"/>
-        <v>94</v>
-      </c>
-      <c r="Q72" s="8"/>
-    </row>
-    <row r="73" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="P72" s="41"/>
+      <c r="Q72" s="21">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="R72" s="8"/>
+    </row>
+    <row r="73" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>29</v>
       </c>
@@ -7745,7 +7897,7 @@
         <v>51</v>
       </c>
       <c r="E73" s="20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73" s="20">
         <v>2</v>
@@ -7772,20 +7924,21 @@
         <v>5</v>
       </c>
       <c r="N73" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O73" s="20">
-        <v>14</v>
-      </c>
-      <c r="P73" s="21">
-        <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-      <c r="Q73" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P73" s="41"/>
+      <c r="Q73" s="21">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="R73" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>29</v>
       </c>
@@ -7831,13 +7984,14 @@
       <c r="O74" s="20">
         <v>45</v>
       </c>
-      <c r="P74" s="21">
-        <f t="shared" ref="P74:P75" si="7">SUM(E74:O74)</f>
+      <c r="P74" s="41"/>
+      <c r="Q74" s="21">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="Q74" s="8"/>
-    </row>
-    <row r="75" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R74" s="8"/>
+    </row>
+    <row r="75" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>29</v>
       </c>
@@ -7872,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M75" s="20">
         <v>5</v>
@@ -7881,17 +8035,18 @@
         <v>7</v>
       </c>
       <c r="O75" s="20">
-        <v>11</v>
-      </c>
-      <c r="P75" s="21">
-        <f t="shared" si="7"/>
-        <v>49</v>
-      </c>
-      <c r="Q75" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="P75" s="41"/>
+      <c r="Q75" s="21">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="R75" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>29</v>
       </c>
@@ -7926,24 +8081,25 @@
         <v>2</v>
       </c>
       <c r="L76" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M76" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="20">
         <v>0</v>
       </c>
       <c r="O76" s="20">
-        <v>18</v>
-      </c>
-      <c r="P76" s="21">
-        <f t="shared" ref="P76:P77" si="8">SUM(E76:O76)</f>
-        <v>42</v>
-      </c>
-      <c r="Q76" s="8"/>
-    </row>
-    <row r="77" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="P76" s="41"/>
+      <c r="Q76" s="21">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="R76" s="8"/>
+    </row>
+    <row r="77" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>29</v>
       </c>
@@ -7981,7 +8137,7 @@
         <v>11</v>
       </c>
       <c r="M77" s="20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N77" s="20">
         <v>3</v>
@@ -7989,15 +8145,16 @@
       <c r="O77" s="20">
         <v>12</v>
       </c>
-      <c r="P77" s="21">
-        <f t="shared" si="8"/>
-        <v>42</v>
-      </c>
-      <c r="Q77" s="8" t="s">
+      <c r="P77" s="41"/>
+      <c r="Q77" s="21">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="R77" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>29</v>
       </c>
@@ -8041,15 +8198,16 @@
         <v>0</v>
       </c>
       <c r="O78" s="20">
-        <v>24</v>
-      </c>
-      <c r="P78" s="21">
-        <f t="shared" ref="P78:P79" si="9">SUM(E78:O78)</f>
-        <v>53</v>
-      </c>
-      <c r="Q78" s="8"/>
-    </row>
-    <row r="79" spans="1:17" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="P78" s="41"/>
+      <c r="Q78" s="21">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="R78" s="8"/>
+    </row>
+    <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>29</v>
       </c>
@@ -8095,15 +8253,16 @@
       <c r="O79" s="20">
         <v>13</v>
       </c>
-      <c r="P79" s="21">
-        <f t="shared" si="9"/>
+      <c r="P79" s="41"/>
+      <c r="Q79" s="21">
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="Q79" s="8" t="s">
+      <c r="R79" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>30</v>
       </c>
@@ -8116,46 +8275,47 @@
       <c r="D80" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E80" s="36">
-        <v>0</v>
-      </c>
-      <c r="F80" s="36">
-        <v>1</v>
-      </c>
-      <c r="G80" s="36">
-        <v>1</v>
-      </c>
-      <c r="H80" s="36">
-        <v>0</v>
-      </c>
-      <c r="I80" s="36">
-        <v>1</v>
-      </c>
-      <c r="J80" s="36">
-        <v>0</v>
-      </c>
-      <c r="K80" s="36">
-        <v>0</v>
-      </c>
-      <c r="L80" s="36">
+      <c r="E80" s="32">
+        <v>0</v>
+      </c>
+      <c r="F80" s="32">
+        <v>1</v>
+      </c>
+      <c r="G80" s="32">
+        <v>1</v>
+      </c>
+      <c r="H80" s="32">
+        <v>0</v>
+      </c>
+      <c r="I80" s="32">
+        <v>1</v>
+      </c>
+      <c r="J80" s="32">
+        <v>0</v>
+      </c>
+      <c r="K80" s="32">
+        <v>0</v>
+      </c>
+      <c r="L80" s="32">
         <v>8</v>
       </c>
-      <c r="M80" s="36">
-        <v>0</v>
-      </c>
-      <c r="N80" s="36">
-        <v>0</v>
-      </c>
-      <c r="O80" s="36">
-        <v>2</v>
-      </c>
-      <c r="P80" s="37">
-        <f t="shared" ref="P80:P85" si="10">SUM(E80:O80)</f>
+      <c r="M80" s="32">
+        <v>0</v>
+      </c>
+      <c r="N80" s="32">
+        <v>0</v>
+      </c>
+      <c r="O80" s="32">
+        <v>2</v>
+      </c>
+      <c r="P80" s="32"/>
+      <c r="Q80" s="21">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="Q80" s="8"/>
-    </row>
-    <row r="81" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="R80" s="8"/>
+    </row>
+    <row r="81" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>30</v>
       </c>
@@ -8168,48 +8328,49 @@
       <c r="D81" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E81" s="36">
+      <c r="E81" s="32">
         <v>10</v>
       </c>
-      <c r="F81" s="36">
+      <c r="F81" s="32">
         <v>3</v>
       </c>
-      <c r="G81" s="36">
-        <v>1</v>
-      </c>
-      <c r="H81" s="36">
-        <v>1</v>
-      </c>
-      <c r="I81" s="36">
-        <v>0</v>
-      </c>
-      <c r="J81" s="36">
-        <v>1</v>
-      </c>
-      <c r="K81" s="36">
-        <v>1</v>
-      </c>
-      <c r="L81" s="36">
+      <c r="G81" s="32">
+        <v>1</v>
+      </c>
+      <c r="H81" s="32">
+        <v>1</v>
+      </c>
+      <c r="I81" s="32">
+        <v>0</v>
+      </c>
+      <c r="J81" s="32">
+        <v>1</v>
+      </c>
+      <c r="K81" s="32">
+        <v>1</v>
+      </c>
+      <c r="L81" s="32">
         <v>12</v>
       </c>
-      <c r="M81" s="36">
+      <c r="M81" s="32">
         <v>5</v>
       </c>
-      <c r="N81" s="36">
+      <c r="N81" s="32">
         <v>11</v>
       </c>
-      <c r="O81" s="36">
+      <c r="O81" s="32">
         <v>21</v>
       </c>
-      <c r="P81" s="37">
-        <f t="shared" si="10"/>
+      <c r="P81" s="32"/>
+      <c r="Q81" s="21">
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="Q81" s="8" t="s">
+      <c r="R81" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>30</v>
       </c>
@@ -8222,46 +8383,47 @@
       <c r="D82" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E82" s="39">
-        <v>0</v>
-      </c>
-      <c r="F82" s="39">
-        <v>2</v>
-      </c>
-      <c r="G82" s="39">
-        <v>1</v>
-      </c>
-      <c r="H82" s="39">
-        <v>0</v>
-      </c>
-      <c r="I82" s="39">
+      <c r="E82" s="15">
+        <v>0</v>
+      </c>
+      <c r="F82" s="15">
+        <v>2</v>
+      </c>
+      <c r="G82" s="15">
+        <v>1</v>
+      </c>
+      <c r="H82" s="15">
+        <v>0</v>
+      </c>
+      <c r="I82" s="15">
         <v>4</v>
       </c>
-      <c r="J82" s="39">
-        <v>0</v>
-      </c>
-      <c r="K82" s="39">
-        <v>1</v>
-      </c>
-      <c r="L82" s="39">
+      <c r="J82" s="15">
+        <v>0</v>
+      </c>
+      <c r="K82" s="15">
+        <v>1</v>
+      </c>
+      <c r="L82" s="15">
         <v>10</v>
       </c>
-      <c r="M82" s="39">
-        <v>0</v>
-      </c>
-      <c r="N82" s="39">
-        <v>0</v>
-      </c>
-      <c r="O82" s="39">
+      <c r="M82" s="15">
+        <v>0</v>
+      </c>
+      <c r="N82" s="15">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15">
         <v>4</v>
       </c>
-      <c r="P82" s="37">
-        <f t="shared" si="10"/>
+      <c r="P82" s="15"/>
+      <c r="Q82" s="21">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="Q82" s="8"/>
-    </row>
-    <row r="83" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="R82" s="8"/>
+    </row>
+    <row r="83" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>30</v>
       </c>
@@ -8274,48 +8436,49 @@
       <c r="D83" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E83" s="41">
+      <c r="E83" s="15">
         <v>13</v>
       </c>
-      <c r="F83" s="41">
-        <v>2</v>
-      </c>
-      <c r="G83" s="41">
-        <v>2</v>
-      </c>
-      <c r="H83" s="41">
-        <v>1</v>
-      </c>
-      <c r="I83" s="41">
-        <v>0</v>
-      </c>
-      <c r="J83" s="41">
-        <v>1</v>
-      </c>
-      <c r="K83" s="41">
-        <v>1</v>
-      </c>
-      <c r="L83" s="41">
+      <c r="F83" s="15">
+        <v>2</v>
+      </c>
+      <c r="G83" s="15">
+        <v>2</v>
+      </c>
+      <c r="H83" s="15">
+        <v>1</v>
+      </c>
+      <c r="I83" s="15">
+        <v>0</v>
+      </c>
+      <c r="J83" s="15">
+        <v>1</v>
+      </c>
+      <c r="K83" s="15">
+        <v>1</v>
+      </c>
+      <c r="L83" s="15">
         <v>13</v>
       </c>
-      <c r="M83" s="41">
+      <c r="M83" s="15">
         <v>8</v>
       </c>
-      <c r="N83" s="41">
+      <c r="N83" s="15">
         <v>14</v>
       </c>
-      <c r="O83" s="41">
+      <c r="O83" s="15">
         <v>29</v>
       </c>
-      <c r="P83" s="37">
-        <f t="shared" si="10"/>
+      <c r="P83" s="15"/>
+      <c r="Q83" s="21">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="Q83" s="8" t="s">
+      <c r="R83" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>30</v>
       </c>
@@ -8361,13 +8524,14 @@
       <c r="O84" s="10">
         <v>3</v>
       </c>
-      <c r="P84" s="37">
-        <f t="shared" si="10"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="21">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="Q84" s="8"/>
-    </row>
-    <row r="85" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="R84" s="8"/>
+    </row>
+    <row r="85" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>30</v>
       </c>
@@ -8407,28 +8571,23 @@
       <c r="M85" s="10">
         <v>4</v>
       </c>
-      <c r="N85" s="38">
+      <c r="N85" s="33">
         <v>8</v>
       </c>
-      <c r="O85" s="38">
+      <c r="O85" s="33">
         <v>25</v>
       </c>
-      <c r="P85" s="37">
-        <f t="shared" si="10"/>
+      <c r="P85" s="33"/>
+      <c r="Q85" s="21">
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="Q85" s="8" t="s">
+      <c r="R85" s="8" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q85" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PRC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R85" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/components/Roster/filled.xlsx
+++ b/src/components/Roster/filled.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYPRO\Roster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYPRO\pzhr_web\src\components\Roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA99B8-F01F-4C22-8F52-78A858D77FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272E051C-68DE-4738-963B-108C9B50E092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97B97223-865E-45D4-9E75-2997D7267C15}"/>
   </bookViews>
@@ -425,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -581,6 +581,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -937,6 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1004,7 +1009,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>17</v>
       </c>
@@ -1055,7 +1060,7 @@
       </c>
       <c r="R2" s="8"/>
     </row>
-    <row r="3" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>17</v>
       </c>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="R3" s="8"/>
     </row>
-    <row r="4" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
         <v>17</v>
       </c>
@@ -1157,7 +1162,7 @@
       </c>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
         <v>17</v>
       </c>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
@@ -1259,7 +1264,7 @@
       </c>
       <c r="R6" s="8"/>
     </row>
-    <row r="7" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>17</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
         <v>17</v>
       </c>
@@ -1363,7 +1368,7 @@
       </c>
       <c r="R8" s="8"/>
     </row>
-    <row r="9" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
         <v>17</v>
       </c>
@@ -1414,7 +1419,7 @@
       </c>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>17</v>
       </c>
@@ -1465,7 +1470,7 @@
       </c>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>17</v>
       </c>
@@ -1518,7 +1523,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>17</v>
       </c>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="R12" s="8"/>
     </row>
-    <row r="13" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>17</v>
       </c>
@@ -1620,7 +1625,7 @@
       </c>
       <c r="R13" s="8"/>
     </row>
-    <row r="14" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
         <v>17</v>
       </c>
@@ -1671,7 +1676,7 @@
       </c>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
         <v>17</v>
       </c>
@@ -1722,7 +1727,7 @@
       </c>
       <c r="R15" s="6"/>
     </row>
-    <row r="16" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>17</v>
       </c>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
         <v>17</v>
       </c>
@@ -1824,7 +1829,7 @@
       </c>
       <c r="R17" s="6"/>
     </row>
-    <row r="18" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>17</v>
       </c>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="R18" s="8"/>
     </row>
-    <row r="19" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>17</v>
       </c>
@@ -1928,7 +1933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>17</v>
       </c>
@@ -2595,7 +2600,7 @@
       </c>
       <c r="R32" s="8"/>
     </row>
-    <row r="33" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
         <v>29</v>
       </c>
@@ -2606,40 +2611,42 @@
       <c r="D33" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="6">
-        <v>1</v>
-      </c>
-      <c r="F33" s="6">
-        <v>1</v>
-      </c>
-      <c r="G33" s="6">
-        <v>1</v>
-      </c>
-      <c r="H33" s="6">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6">
-        <v>0</v>
-      </c>
-      <c r="K33" s="6">
-        <v>0</v>
-      </c>
-      <c r="L33" s="6">
-        <v>0</v>
-      </c>
-      <c r="M33" s="6">
-        <v>0</v>
-      </c>
-      <c r="N33" s="6">
-        <v>0</v>
-      </c>
-      <c r="O33" s="6">
-        <v>16</v>
-      </c>
-      <c r="P33" s="6"/>
+      <c r="E33" s="5">
+        <v>1</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <v>15</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1</v>
+      </c>
       <c r="Q33" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2657,40 +2664,42 @@
       <c r="D34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <v>6</v>
       </c>
-      <c r="F34" s="6">
-        <v>2</v>
-      </c>
-      <c r="G34" s="6">
-        <v>2</v>
-      </c>
-      <c r="H34" s="6">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6">
-        <v>3</v>
-      </c>
-      <c r="J34" s="6">
-        <v>1</v>
-      </c>
-      <c r="K34" s="6">
-        <v>0</v>
-      </c>
-      <c r="L34" s="6">
-        <v>0</v>
-      </c>
-      <c r="M34" s="6">
-        <v>0</v>
-      </c>
-      <c r="N34" s="6">
-        <v>0</v>
-      </c>
-      <c r="O34" s="6">
-        <v>103</v>
-      </c>
-      <c r="P34" s="6"/>
+      <c r="F34" s="5">
+        <v>2</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <v>2</v>
+      </c>
+      <c r="J34" s="5">
+        <v>1</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5">
+        <v>101</v>
+      </c>
+      <c r="P34" s="6">
+        <v>4</v>
+      </c>
       <c r="Q34" s="3">
         <f t="shared" si="0"/>
         <v>117</v>
@@ -2838,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" s="5">
         <v>80</v>
@@ -2846,7 +2855,7 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="3">
         <f t="shared" si="0"/>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R37" s="8"/>
     </row>
@@ -2865,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -2883,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="5">
         <v>0</v>
@@ -2892,12 +2901,12 @@
         <v>1</v>
       </c>
       <c r="O38" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="3">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R38" s="8" t="s">
         <v>58</v>
@@ -2954,7 +2963,7 @@
       </c>
       <c r="R39" s="8"/>
     </row>
-    <row r="40" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
         <v>30</v>
       </c>
@@ -3005,7 +3014,7 @@
       </c>
       <c r="R40" s="43"/>
     </row>
-    <row r="41" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="37" t="s">
         <v>30</v>
       </c>
@@ -3056,7 +3065,7 @@
       </c>
       <c r="R41" s="43"/>
     </row>
-    <row r="42" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37" t="s">
         <v>30</v>
       </c>
@@ -3107,7 +3116,7 @@
       </c>
       <c r="R42" s="43"/>
     </row>
-    <row r="43" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>30</v>
       </c>
@@ -3158,7 +3167,7 @@
       </c>
       <c r="R43" s="43"/>
     </row>
-    <row r="44" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
         <v>30</v>
       </c>
@@ -3209,7 +3218,7 @@
       </c>
       <c r="R44" s="43"/>
     </row>
-    <row r="45" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
         <v>30</v>
       </c>
@@ -3262,7 +3271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="37" t="s">
         <v>30</v>
       </c>
@@ -3313,7 +3322,7 @@
       </c>
       <c r="R46" s="43"/>
     </row>
-    <row r="47" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="37" t="s">
         <v>30</v>
       </c>
@@ -3364,7 +3373,7 @@
       </c>
       <c r="R47" s="43"/>
     </row>
-    <row r="48" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="37" t="s">
         <v>30</v>
       </c>
@@ -3415,7 +3424,7 @@
       </c>
       <c r="R48" s="43"/>
     </row>
-    <row r="49" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="37" t="s">
         <v>30</v>
       </c>
@@ -3468,7 +3477,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37" t="s">
         <v>30</v>
       </c>
@@ -3521,7 +3530,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="37" t="s">
         <v>30</v>
       </c>
@@ -3572,7 +3581,7 @@
       </c>
       <c r="R51" s="43"/>
     </row>
-    <row r="52" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
         <v>30</v>
       </c>
@@ -3623,7 +3632,7 @@
       </c>
       <c r="R52" s="43"/>
     </row>
-    <row r="53" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>30</v>
       </c>
@@ -3676,7 +3685,7 @@
       </c>
       <c r="R53" s="43"/>
     </row>
-    <row r="54" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="37" t="s">
         <v>30</v>
       </c>
@@ -3727,7 +3736,7 @@
       </c>
       <c r="R54" s="43"/>
     </row>
-    <row r="55" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="37" t="s">
         <v>30</v>
       </c>
@@ -3778,7 +3787,7 @@
       </c>
       <c r="R55" s="43"/>
     </row>
-    <row r="56" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="37" t="s">
         <v>30</v>
       </c>
@@ -3829,7 +3838,7 @@
       </c>
       <c r="R56" s="43"/>
     </row>
-    <row r="57" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="37" t="s">
         <v>30</v>
       </c>
@@ -3880,7 +3889,7 @@
       </c>
       <c r="R57" s="43"/>
     </row>
-    <row r="58" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37" t="s">
         <v>30</v>
       </c>
@@ -3933,7 +3942,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
         <v>30</v>
       </c>
@@ -3987,7 +3996,13 @@
       <c r="R59" s="43"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R59" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}"/>
+  <autoFilter ref="A1:R59" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="GKUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3995,6 +4010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4060,7 +4076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -4113,7 +4129,7 @@
       </c>
       <c r="R2" s="8"/>
     </row>
-    <row r="3" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -4168,7 +4184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -4221,7 +4237,7 @@
       </c>
       <c r="R4" s="8"/>
     </row>
-    <row r="5" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -4276,7 +4292,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -4329,7 +4345,7 @@
       </c>
       <c r="R6" s="8"/>
     </row>
-    <row r="7" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -4384,7 +4400,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -4437,7 +4453,7 @@
       </c>
       <c r="R8" s="8"/>
     </row>
-    <row r="9" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -4492,7 +4508,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -4545,7 +4561,7 @@
       </c>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -5032,7 +5048,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -5085,7 +5101,7 @@
       </c>
       <c r="R20" s="8"/>
     </row>
-    <row r="21" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -5140,7 +5156,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -5193,7 +5209,7 @@
       </c>
       <c r="R22" s="8"/>
     </row>
-    <row r="23" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -5248,7 +5264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -5301,7 +5317,7 @@
       </c>
       <c r="R24" s="8"/>
     </row>
-    <row r="25" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -5356,7 +5372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -5409,7 +5425,7 @@
       </c>
       <c r="R26" s="8"/>
     </row>
-    <row r="27" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -5466,7 +5482,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -5519,7 +5535,7 @@
       </c>
       <c r="R28" s="8"/>
     </row>
-    <row r="29" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -5574,7 +5590,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -5627,7 +5643,7 @@
       </c>
       <c r="R30" s="8"/>
     </row>
-    <row r="31" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -5682,7 +5698,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
@@ -5735,7 +5751,7 @@
       </c>
       <c r="R32" s="8"/>
     </row>
-    <row r="33" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -5790,7 +5806,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>17</v>
       </c>
@@ -5843,7 +5859,7 @@
       </c>
       <c r="R34" s="8"/>
     </row>
-    <row r="35" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
@@ -6330,7 +6346,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>30</v>
       </c>
@@ -6383,7 +6399,7 @@
       </c>
       <c r="R44" s="8"/>
     </row>
-    <row r="45" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>30</v>
       </c>
@@ -6438,7 +6454,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
@@ -6491,7 +6507,7 @@
       </c>
       <c r="R46" s="8"/>
     </row>
-    <row r="47" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>30</v>
       </c>
@@ -6546,7 +6562,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>30</v>
       </c>
@@ -6599,7 +6615,7 @@
       </c>
       <c r="R48" s="8"/>
     </row>
-    <row r="49" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>30</v>
       </c>
@@ -6654,7 +6670,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -6707,7 +6723,7 @@
       </c>
       <c r="R50" s="8"/>
     </row>
-    <row r="51" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>17</v>
       </c>
@@ -6760,7 +6776,7 @@
       </c>
       <c r="R51" s="8"/>
     </row>
-    <row r="52" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>17</v>
       </c>
@@ -6813,7 +6829,7 @@
       </c>
       <c r="R52" s="8"/>
     </row>
-    <row r="53" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>17</v>
       </c>
@@ -6866,7 +6882,7 @@
       </c>
       <c r="R53" s="8"/>
     </row>
-    <row r="54" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>17</v>
       </c>
@@ -7131,7 +7147,7 @@
       </c>
       <c r="R58" s="8"/>
     </row>
-    <row r="59" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>30</v>
       </c>
@@ -7144,37 +7160,37 @@
       <c r="D59" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E59" s="22">
-        <v>2</v>
-      </c>
-      <c r="F59" s="22">
-        <v>2</v>
-      </c>
-      <c r="G59" s="22">
-        <v>0</v>
-      </c>
-      <c r="H59" s="22">
-        <v>0</v>
-      </c>
-      <c r="I59" s="22">
-        <v>0</v>
-      </c>
-      <c r="J59" s="22">
-        <v>0</v>
-      </c>
-      <c r="K59" s="22">
-        <v>1</v>
-      </c>
-      <c r="L59" s="22">
-        <v>0</v>
-      </c>
-      <c r="M59" s="22">
-        <v>0</v>
-      </c>
-      <c r="N59" s="22">
-        <v>0</v>
-      </c>
-      <c r="O59" s="22">
+      <c r="E59" s="48">
+        <v>2</v>
+      </c>
+      <c r="F59" s="48">
+        <v>2</v>
+      </c>
+      <c r="G59" s="48">
+        <v>0</v>
+      </c>
+      <c r="H59" s="48">
+        <v>0</v>
+      </c>
+      <c r="I59" s="48">
+        <v>0</v>
+      </c>
+      <c r="J59" s="48">
+        <v>0</v>
+      </c>
+      <c r="K59" s="48">
+        <v>1</v>
+      </c>
+      <c r="L59" s="48">
+        <v>0</v>
+      </c>
+      <c r="M59" s="48">
+        <v>0</v>
+      </c>
+      <c r="N59" s="48">
+        <v>0</v>
+      </c>
+      <c r="O59" s="48">
         <v>103</v>
       </c>
       <c r="P59" s="22"/>
@@ -7184,7 +7200,7 @@
       </c>
       <c r="R59" s="8"/>
     </row>
-    <row r="60" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>30</v>
       </c>
@@ -7237,7 +7253,7 @@
       </c>
       <c r="R60" s="8"/>
     </row>
-    <row r="61" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>30</v>
       </c>
@@ -7250,37 +7266,37 @@
       <c r="D61" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="5">
         <v>7</v>
       </c>
-      <c r="F61" s="11">
-        <v>1</v>
-      </c>
-      <c r="G61" s="11">
-        <v>1</v>
-      </c>
-      <c r="H61" s="11">
-        <v>1</v>
-      </c>
-      <c r="I61" s="11">
-        <v>1</v>
-      </c>
-      <c r="J61" s="11">
-        <v>2</v>
-      </c>
-      <c r="K61" s="11">
+      <c r="F61" s="5">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5">
+        <v>1</v>
+      </c>
+      <c r="H61" s="5">
+        <v>1</v>
+      </c>
+      <c r="I61" s="5">
+        <v>1</v>
+      </c>
+      <c r="J61" s="5">
+        <v>2</v>
+      </c>
+      <c r="K61" s="5">
         <v>3</v>
       </c>
-      <c r="L61" s="11">
-        <v>0</v>
-      </c>
-      <c r="M61" s="11">
-        <v>0</v>
-      </c>
-      <c r="N61" s="11">
-        <v>0</v>
-      </c>
-      <c r="O61" s="11">
+      <c r="L61" s="5">
+        <v>0</v>
+      </c>
+      <c r="M61" s="5">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5">
+        <v>0</v>
+      </c>
+      <c r="O61" s="5">
         <v>106</v>
       </c>
       <c r="P61" s="11"/>
@@ -7290,7 +7306,7 @@
       </c>
       <c r="R61" s="8"/>
     </row>
-    <row r="62" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>17</v>
       </c>
@@ -7343,7 +7359,7 @@
       </c>
       <c r="R62" s="8"/>
     </row>
-    <row r="63" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -7398,7 +7414,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>17</v>
       </c>
@@ -7451,7 +7467,7 @@
       </c>
       <c r="R64" s="8"/>
     </row>
-    <row r="65" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>17</v>
       </c>
@@ -7506,7 +7522,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>17</v>
       </c>
@@ -7559,7 +7575,7 @@
       </c>
       <c r="R66" s="8"/>
     </row>
-    <row r="67" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -7614,7 +7630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>17</v>
       </c>
@@ -7667,7 +7683,7 @@
       </c>
       <c r="R68" s="8"/>
     </row>
-    <row r="69" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>17</v>
       </c>
@@ -7722,7 +7738,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>17</v>
       </c>
@@ -7775,7 +7791,7 @@
       </c>
       <c r="R70" s="8"/>
     </row>
-    <row r="71" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>17</v>
       </c>
@@ -8262,7 +8278,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>30</v>
       </c>
@@ -8315,7 +8331,7 @@
       </c>
       <c r="R80" s="8"/>
     </row>
-    <row r="81" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>30</v>
       </c>
@@ -8370,7 +8386,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>30</v>
       </c>
@@ -8423,7 +8439,7 @@
       </c>
       <c r="R82" s="8"/>
     </row>
-    <row r="83" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>30</v>
       </c>
@@ -8478,7 +8494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>30</v>
       </c>
@@ -8531,7 +8547,7 @@
       </c>
       <c r="R84" s="8"/>
     </row>
-    <row r="85" spans="1:18" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>30</v>
       </c>
@@ -8587,7 +8603,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R85" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}"/>
+  <autoFilter ref="A1:R85" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="GKUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
